--- a/DocProyecto/_Proyecto.xlsx
+++ b/DocProyecto/_Proyecto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Willy\UniversidadGalileo\PrepPrivados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Willy\UniversidadGalileo\PrepPrivados\SysDoc\maru-crm\DocProyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03836F2A-3904-4A79-8E16-C9AD20ACB51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B677A45B-5E07-4AD5-BB45-3021C1191023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -21,18 +21,32 @@
     <sheet name="Hoja6" sheetId="6" r:id="rId6"/>
     <sheet name="Hoja7" sheetId="7" r:id="rId7"/>
     <sheet name="Hoja8" sheetId="8" r:id="rId8"/>
+    <sheet name="Hoja9" sheetId="9" r:id="rId9"/>
+    <sheet name="Hoja10" sheetId="10" r:id="rId10"/>
+    <sheet name="Hoja11" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="1534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="1708">
   <si>
     <t>ACTIVIDAD</t>
   </si>
@@ -4634,6 +4648,528 @@
   </si>
   <si>
     <t>+$210</t>
+  </si>
+  <si>
+    <t>Tenants (agencias)</t>
+  </si>
+  <si>
+    <t>Agentes concurrentes</t>
+  </si>
+  <si>
+    <t>Tráfico portal/mes</t>
+  </si>
+  <si>
+    <t>Mínima ($144)</t>
+  </si>
+  <si>
+    <t>$144</t>
+  </si>
+  <si>
+    <t>1 – 5</t>
+  </si>
+  <si>
+    <t>hasta 15</t>
+  </si>
+  <si>
+    <t>hasta 300</t>
+  </si>
+  <si>
+    <t>Óptima ($354)</t>
+  </si>
+  <si>
+    <t>$354</t>
+  </si>
+  <si>
+    <t>5 – 20</t>
+  </si>
+  <si>
+    <t>hasta 60</t>
+  </si>
+  <si>
+    <t>hasta 2 000</t>
+  </si>
+  <si>
+    <t>5 000 visitas</t>
+  </si>
+  <si>
+    <t>30 000 visitas</t>
+  </si>
+  <si>
+    <t>Especificación referencial</t>
+  </si>
+  <si>
+    <t>Costo (USD)</t>
+  </si>
+  <si>
+    <t>Observación</t>
+  </si>
+  <si>
+    <t>Laptop desarrollador</t>
+  </si>
+  <si>
+    <t>16 GB RAM · SSD 512 GB · CPU 8+ cores (Dell Inspiron 15 / Lenovo IdeaPad / MacBook Air M2)</t>
+  </si>
+  <si>
+    <t>$900</t>
+  </si>
+  <si>
+    <t>Monitor externo 24"</t>
+  </si>
+  <si>
+    <t>FHD IPS, para trabajo en pantalla dual</t>
+  </si>
+  <si>
+    <t>UPS / regulador de voltaje</t>
+  </si>
+  <si>
+    <t>APC Back-UPS 600 VA o similar</t>
+  </si>
+  <si>
+    <t>$60</t>
+  </si>
+  <si>
+    <t>Mouse + teclado</t>
+  </si>
+  <si>
+    <t>Periféricos básicos</t>
+  </si>
+  <si>
+    <t>$30</t>
+  </si>
+  <si>
+    <t>Subtotal hardware</t>
+  </si>
+  <si>
+    <t>$1 120</t>
+  </si>
+  <si>
+    <t>Duración</t>
+  </si>
+  <si>
+    <t>GitHub Teams</t>
+  </si>
+  <si>
+    <t>$4/usuario/mes × 2 usuarios</t>
+  </si>
+  <si>
+    <t>4 meses</t>
+  </si>
+  <si>
+    <t>$32</t>
+  </si>
+  <si>
+    <t>CI/CD + repos privados; free tier disponible para equipos pequeños</t>
+  </si>
+  <si>
+    <t>Figma (diseño UI/UX)</t>
+  </si>
+  <si>
+    <t>Professional $12/mes × 1 usuario</t>
+  </si>
+  <si>
+    <t>$48</t>
+  </si>
+  <si>
+    <t>Opcional; el plan gratuito cubre la fase de wireframes</t>
+  </si>
+  <si>
+    <t>Zoom Pro</t>
+  </si>
+  <si>
+    <t>$15/mes × 1 cuenta</t>
+  </si>
+  <si>
+    <t>Para reuniones con el cliente; la versión gratuita limita a 40 min</t>
+  </si>
+  <si>
+    <t>Dominio (.com o .gt)</t>
+  </si>
+  <si>
+    <t>Registro anual (GoDaddy / Namecheap)</t>
+  </si>
+  <si>
+    <t>1 año</t>
+  </si>
+  <si>
+    <t>gestpro.com o gestpro.gt; necesario desde el inicio</t>
+  </si>
+  <si>
+    <t>Subtotal herramientas</t>
+  </si>
+  <si>
+    <t>$155</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Herramientas y suscripciones</t>
+  </si>
+  <si>
+    <t>Infraestructura staging</t>
+  </si>
+  <si>
+    <t>Hardware de trabajo</t>
+  </si>
+  <si>
+    <t>Total con hardware</t>
+  </si>
+  <si>
+    <t>$21 905</t>
+  </si>
+  <si>
+    <t>Recurso humano</t>
+  </si>
+  <si>
+    <t>Producto GCP</t>
+  </si>
+  <si>
+    <t>Servidor staging</t>
+  </si>
+  <si>
+    <t>e2-micro + 20 GB SSD</t>
+  </si>
+  <si>
+    <t>$20</t>
+  </si>
+  <si>
+    <t>Cloud SQL staging</t>
+  </si>
+  <si>
+    <t>db-f1-micro PostgreSQL</t>
+  </si>
+  <si>
+    <t>$40</t>
+  </si>
+  <si>
+    <t>Redis staging</t>
+  </si>
+  <si>
+    <t>Upstash free tier</t>
+  </si>
+  <si>
+    <t>Subtotal infraestructura staging</t>
+  </si>
+  <si>
+    <t>| Rubro | Año 1 | Año 2 | Año 3 | Año 4 | Año 5 |</t>
+  </si>
+  <si>
+    <t>|:------|------:|------:|------:|------:|------:|</t>
+  </si>
+  <si>
+    <t>| Desarrollador de soporte (10 h/sem · 520 h/año · $15/h) | $7 800 | $7 800 | $7 800 | $7 800 | $7 800 |</t>
+  </si>
+  <si>
+    <t>| Infraestructura (VPS Hetzner + dominio SSL) | $130 | $130 | $220 | $220 | $400 |</t>
+  </si>
+  <si>
+    <t>| Servicios de terceros (Resend, Mapbox, Sentry) | $300 | $600 | $720 | $1 200 | $1 200 |</t>
+  </si>
+  <si>
+    <t>| Actualizaciones de seguridad / dependencias | $500 | $300 | $300 | $300 | $300 |</t>
+  </si>
+  <si>
+    <t>| Contingencia (10 %) | $873 | $883 | $904 | $952 | $970 |</t>
+  </si>
+  <si>
+    <t>| **Total año (USD)** | **$9 603** | **$9 713** | **$9 944** | **$10 472** | **$10 670** |</t>
+  </si>
+  <si>
+    <t>| **Acumulado (USD)** | $9 603 | $19 316 | $29 260 | $39 732 | **$50 402** |</t>
+  </si>
+  <si>
+    <t>Desarrollador de soporte (10 h/sem · 520 h/año · $15/h)</t>
+  </si>
+  <si>
+    <t>$7 800</t>
+  </si>
+  <si>
+    <t>$873</t>
+  </si>
+  <si>
+    <t>$883</t>
+  </si>
+  <si>
+    <t>$904</t>
+  </si>
+  <si>
+    <t>$952</t>
+  </si>
+  <si>
+    <t>$970</t>
+  </si>
+  <si>
+    <t>$9 603</t>
+  </si>
+  <si>
+    <t>$9 713</t>
+  </si>
+  <si>
+    <t>$9 944</t>
+  </si>
+  <si>
+    <t>$10 472</t>
+  </si>
+  <si>
+    <t>$10 670</t>
+  </si>
+  <si>
+    <t>$19 316</t>
+  </si>
+  <si>
+    <t>$29 260</t>
+  </si>
+  <si>
+    <t>$39 732</t>
+  </si>
+  <si>
+    <t>$50 402</t>
+  </si>
+  <si>
+    <t>Año 0</t>
+  </si>
+  <si>
+    <t>Inversión inicial (desarrollo)</t>
+  </si>
+  <si>
+    <t>−$20,570</t>
+  </si>
+  <si>
+    <t>Ingresos anuales</t>
+  </si>
+  <si>
+    <t>$7,860</t>
+  </si>
+  <si>
+    <t>$20,712</t>
+  </si>
+  <si>
+    <t>$36,600</t>
+  </si>
+  <si>
+    <t>$53,568</t>
+  </si>
+  <si>
+    <t>$70,704</t>
+  </si>
+  <si>
+    <t>Costos de mantenimiento (§2.7)</t>
+  </si>
+  <si>
+    <t>$9,603</t>
+  </si>
+  <si>
+    <t>$9,713</t>
+  </si>
+  <si>
+    <t>$9,944</t>
+  </si>
+  <si>
+    <t>$10,472</t>
+  </si>
+  <si>
+    <t>$10,670</t>
+  </si>
+  <si>
+    <t>Flujo neto del período</t>
+  </si>
+  <si>
+    <t>−$1,743</t>
+  </si>
+  <si>
+    <t>+$10,999</t>
+  </si>
+  <si>
+    <t>+$26,656</t>
+  </si>
+  <si>
+    <t>+$43,096</t>
+  </si>
+  <si>
+    <t>+$60,034</t>
+  </si>
+  <si>
+    <t>Flujo acumulado</t>
+  </si>
+  <si>
+    <t>−$22,313</t>
+  </si>
+  <si>
+    <t>−$11,314</t>
+  </si>
+  <si>
+    <t>+$15,342 ✅</t>
+  </si>
+  <si>
+    <t>+$58,438</t>
+  </si>
+  <si>
+    <t>+$118,472</t>
+  </si>
+  <si>
+    <t>Starter (~$45/mes)</t>
+  </si>
+  <si>
+    <t>$45</t>
+  </si>
+  <si>
+    <t>Profesional (~$104/mes)</t>
+  </si>
+  <si>
+    <t>$104</t>
+  </si>
+  <si>
+    <t>Empresarial (~$208/mes)</t>
+  </si>
+  <si>
+    <t>$208</t>
+  </si>
+  <si>
+    <t>Starter (aporte mensual)</t>
+  </si>
+  <si>
+    <t>$135</t>
+  </si>
+  <si>
+    <t>$270</t>
+  </si>
+  <si>
+    <t>$450</t>
+  </si>
+  <si>
+    <t>Profesional (aporte mensual)</t>
+  </si>
+  <si>
+    <t>$312</t>
+  </si>
+  <si>
+    <t>$832</t>
+  </si>
+  <si>
+    <t>$1,560</t>
+  </si>
+  <si>
+    <t>$2,080</t>
+  </si>
+  <si>
+    <t>$2,912</t>
+  </si>
+  <si>
+    <t>Empresarial (aporte mensual)</t>
+  </si>
+  <si>
+    <t>$624</t>
+  </si>
+  <si>
+    <t>$1,040</t>
+  </si>
+  <si>
+    <t>$1,664</t>
+  </si>
+  <si>
+    <t>MRR total</t>
+  </si>
+  <si>
+    <t>$655</t>
+  </si>
+  <si>
+    <t>$1,726</t>
+  </si>
+  <si>
+    <t>$3,050</t>
+  </si>
+  <si>
+    <t>$4,464</t>
+  </si>
+  <si>
+    <t>$5,892</t>
+  </si>
+  <si>
+    <t>Ingreso anual (MRR × 12)</t>
+  </si>
+  <si>
+    <t>AÑO 1</t>
+  </si>
+  <si>
+    <t>AÑO 2</t>
+  </si>
+  <si>
+    <t>AÑO 3</t>
+  </si>
+  <si>
+    <t>AÑO 4</t>
+  </si>
+  <si>
+    <t>AÑO 5</t>
+  </si>
+  <si>
+    <t>AÑO 0</t>
+  </si>
+  <si>
+    <t>Gratuito</t>
+  </si>
+  <si>
+    <t>* 1 agentes</t>
+  </si>
+  <si>
+    <t>* 5 Propiedades</t>
+  </si>
+  <si>
+    <t>* Portal Público</t>
+  </si>
+  <si>
+    <t>* 3 agentes</t>
+  </si>
+  <si>
+    <t>* 25 Propiedades</t>
+  </si>
+  <si>
+    <t>* 5 agentes</t>
+  </si>
+  <si>
+    <t>* 100 Propiedades</t>
+  </si>
+  <si>
+    <t>* 25 agentes</t>
+  </si>
+  <si>
+    <t>* 500 Propiedades</t>
+  </si>
+  <si>
+    <t>* Brochures Pdf</t>
+  </si>
+  <si>
+    <t>* App Movil</t>
+  </si>
+  <si>
+    <t>* Func. del plan Profesional</t>
+  </si>
+  <si>
+    <t>* Plataformas Externas</t>
+  </si>
+  <si>
+    <t>Costo Inicial</t>
+  </si>
+  <si>
+    <t>Costo Soporte Anual</t>
+  </si>
+  <si>
+    <t>Costos Mant. Anual</t>
+  </si>
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>Costos</t>
+  </si>
+  <si>
+    <t>Ingresos</t>
+  </si>
+  <si>
+    <t>Costos Acomulados</t>
+  </si>
+  <si>
+    <t>Ingresos Acumulados</t>
   </si>
 </sst>
 </file>
@@ -4643,7 +5179,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;Q&quot;#,##0;[Red]\-&quot;Q&quot;#,##0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4700,8 +5236,31 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4756,8 +5315,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -4861,11 +5444,171 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF002060"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF002060"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF002060"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF002060"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF002060"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF002060"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF002060"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF002060"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF002060"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4996,6 +5739,9 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5023,11 +5769,149 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="125">
+  <dxfs count="175">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -5047,6 +5931,627 @@
           <bgColor rgb="FF002060"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -5881,245 +7386,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -6139,135 +7405,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -6316,39 +7453,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -6372,15 +7489,31 @@
           <bgColor rgb="FF002060"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6401,10 +7534,53 @@
           <bgColor rgb="FF002060"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF03AD13"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -6414,6 +7590,2295 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-GT" b="1" i="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Costos Iniciales y Anual del Proyecto</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-GT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-8A03-447E-AB83-7364AE4E3F74}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-8A03-447E-AB83-7364AE4E3F74}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.5555555555555552E-2"/>
+                  <c:y val="0.20833333333333334"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                  <a:extLst>
+                    <a:ext uri="{C807C97D-BFC1-408E-A445-0C87EB9F89A2}">
+                      <ask:lineSketchStyleProps xmlns:ask="http://schemas.microsoft.com/office/drawing/2018/sketchyshapes" sd="0">
+                        <a:custGeom>
+                          <a:avLst/>
+                          <a:gdLst/>
+                          <a:ahLst/>
+                          <a:cxnLst/>
+                          <a:rect l="0" t="0" r="0" b="0"/>
+                          <a:pathLst/>
+                        </a:custGeom>
+                        <ask:type/>
+                      </ask:lineSketchStyleProps>
+                    </a:ext>
+                  </a:extLst>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-GT"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst>
+                        <a:gd name="adj1" fmla="val 72918"/>
+                        <a:gd name="adj2" fmla="val -39955"/>
+                      </a:avLst>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-8A03-447E-AB83-7364AE4E3F74}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.13055555555555554"/>
+                  <c:y val="4.3981481481481483E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                    <a:noAutofit/>
+                  </a:bodyPr>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="dk1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:fld id="{A29D5E8F-6583-45F5-AA85-B1435AAAC429}" type="CATEGORYNAME">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr>
+                        <a:defRPr/>
+                      </a:pPr>
+                      <a:t>[NOMBRE DE CATEGORÍA]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t> </a:t>
+                    </a:r>
+                    <a:fld id="{8FC45909-9823-4BDB-B6EA-E5B917C08F2F}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:pPr>
+                        <a:defRPr/>
+                      </a:pPr>
+                      <a:t>[PORCENTAJE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:noAutofit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-GT"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.20258683289588802"/>
+                      <c:h val="0.11715806357538641"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-8A03-447E-AB83-7364AE4E3F74}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:sysClr val="window" lastClr="FFFFFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-GT"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <a:prstGeom prst="wedgeRectCallout">
+                    <a:avLst/>
+                  </a:prstGeom>
+                  <a:noFill/>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                </c15:spPr>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja11!$B$3:$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Costo Inicial</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Costo Soporte Anual</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Costos Mant. Anual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja11!$C$3:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>20570</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8A03-447E-AB83-7364AE4E3F74}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-GT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill>
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="74000">
+          <a:schemeClr val="accent5">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="83000">
+          <a:schemeClr val="accent5">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:srgbClr val="002060"/>
+        </a:gs>
+      </a:gsLst>
+      <a:lin ang="5400000" scaled="1"/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-GT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-GT" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Punto de Equilibrio</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.38580555555555551"/>
+          <c:y val="2.7777777777777776E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-GT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja11!$C$53</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Costos Acomulados</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="44450" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja11!$B$54:$B$59</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Año 0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Año 1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Año 2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Año 3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Año 4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Año 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja11!$C$54:$C$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>20.57</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.172999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.886000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>49.83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60.302</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70.971999999999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CB42-45CE-8343-14F18EFFBF5A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja11!$D$53</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ingresos Acumulados</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="47625" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="03AD13"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja11!$B$54:$B$59</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Año 0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Año 1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Año 2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Año 3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Año 4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Año 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja11!$D$54:$D$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.86</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28.571999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>65.171999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>118.74</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>189.44399999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CB42-45CE-8343-14F18EFFBF5A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="787806464"/>
+        <c:axId val="787808384"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="787806464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-GT"/>
+                  <a:t>Año</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-GT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-GT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="787808384"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="787808384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-GT"/>
+                  <a:t>Miles de $</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="bg1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-GT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-GT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="787806464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-GT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill>
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="17000">
+          <a:schemeClr val="accent5">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="61000">
+          <a:schemeClr val="accent5">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="80000">
+          <a:srgbClr val="002060"/>
+        </a:gs>
+      </a:gsLst>
+      <a:lin ang="5400000" scaled="1"/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400" b="1" i="0" baseline="0">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-GT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6601,8 +10066,240 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>784860</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{139AB9D4-AD99-03AF-F67F-1E7F5CE6F4AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="3253740"/>
+          <a:ext cx="7642860" cy="2567940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88C41BF4-48B8-D530-3820-DEC611270574}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>91439</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>12431</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43E3EF84-CF2E-14D3-FFD2-2298D82FF728}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect l="1995" r="6591"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883919" y="4206240"/>
+          <a:ext cx="4191001" cy="2755631"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A42BA43-D82D-2578-C24B-45C3F28C879C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>713912</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>79619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70FD6D36-525A-7525-7A4B-E7FDBC030E03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6103620" y="14264640"/>
+          <a:ext cx="7846232" cy="4285859"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{55B3C92D-07CA-4015-8A52-A029A62B815E}" name="Tabla1" displayName="Tabla1" ref="B4:F16" totalsRowShown="0" headerRowDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{55B3C92D-07CA-4015-8A52-A029A62B815E}" name="Tabla1" displayName="Tabla1" ref="B4:F16" totalsRowShown="0" headerRowDxfId="146">
   <autoFilter ref="B4:F16" xr:uid="{55B3C92D-07CA-4015-8A52-A029A62B815E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{EC45B9AD-8128-4DB7-B733-82E5D007823A}" name="ACTIVIDAD"/>
@@ -6616,7 +10313,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C6A9A236-E597-41ED-9B9D-4FCA5CFCAB7D}" name="Tabla11" displayName="Tabla11" ref="C112:D142" totalsRowShown="0" headerRowDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C6A9A236-E597-41ED-9B9D-4FCA5CFCAB7D}" name="Tabla11" displayName="Tabla11" ref="C112:D142" totalsRowShown="0" headerRowDxfId="135">
   <autoFilter ref="C112:D142" xr:uid="{C6A9A236-E597-41ED-9B9D-4FCA5CFCAB7D}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{838FC612-16ED-4282-8A68-8E65968BE0FC}" name="No."/>
@@ -6627,81 +10324,81 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{43B5C32A-C8F9-440F-B2F2-C6ADDC849102}" name="Tabla4" displayName="Tabla4" ref="C144:E148" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{43B5C32A-C8F9-440F-B2F2-C6ADDC849102}" name="Tabla4" displayName="Tabla4" ref="C144:E148" totalsRowShown="0" headerRowDxfId="134" dataDxfId="133">
   <autoFilter ref="C144:E148" xr:uid="{43B5C32A-C8F9-440F-B2F2-C6ADDC849102}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{63D79985-9964-4478-85A2-4AA2EA86ABFD}" name="Símbolo" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{586FC4E8-6370-4465-851D-8BA5AF9F1B8B}" name="Término" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{E89652BC-59DE-4E89-A1B8-8AB5C2552CB2}" name="Significado" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{63D79985-9964-4478-85A2-4AA2EA86ABFD}" name="Símbolo" dataDxfId="132"/>
+    <tableColumn id="2" xr3:uid="{586FC4E8-6370-4465-851D-8BA5AF9F1B8B}" name="Término" dataDxfId="131"/>
+    <tableColumn id="3" xr3:uid="{E89652BC-59DE-4E89-A1B8-8AB5C2552CB2}" name="Significado" dataDxfId="130"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F6A305F0-44D2-4DB5-B707-CB107EBDB572}" name="Tabla12" displayName="Tabla12" ref="C154:G184" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F6A305F0-44D2-4DB5-B707-CB107EBDB572}" name="Tabla12" displayName="Tabla12" ref="C154:G184" totalsRowShown="0" headerRowDxfId="129" dataDxfId="128">
   <autoFilter ref="C154:G184" xr:uid="{F6A305F0-44D2-4DB5-B707-CB107EBDB572}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3D31C8C0-E3D1-49F3-9A9C-A219B0B41EA8}" name="Código" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{C2FA137A-28E8-48BE-B040-09108A570141}" name="Historia (resumen)" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{83807629-4684-4468-A306-028EDFB5F7F7}" name="Épica / Módulo" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{190A189F-1386-4E5B-AD12-C47C1299BD63}" name="Prioridad" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{3F1FFDFA-8572-4F18-9340-CC7F37C54013}" name="Dependencias" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{3D31C8C0-E3D1-49F3-9A9C-A219B0B41EA8}" name="Código" dataDxfId="127"/>
+    <tableColumn id="2" xr3:uid="{C2FA137A-28E8-48BE-B040-09108A570141}" name="Historia (resumen)" dataDxfId="126"/>
+    <tableColumn id="3" xr3:uid="{83807629-4684-4468-A306-028EDFB5F7F7}" name="Épica / Módulo" dataDxfId="125"/>
+    <tableColumn id="4" xr3:uid="{190A189F-1386-4E5B-AD12-C47C1299BD63}" name="Prioridad" dataDxfId="124"/>
+    <tableColumn id="5" xr3:uid="{3F1FFDFA-8572-4F18-9340-CC7F37C54013}" name="Dependencias" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{AACB38A0-A41E-4166-B442-690624D094D9}" name="Tabla13" displayName="Tabla13" ref="C3:D62" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{AACB38A0-A41E-4166-B442-690624D094D9}" name="Tabla13" displayName="Tabla13" ref="C3:D62" totalsRowShown="0" headerRowDxfId="122" dataDxfId="121">
   <autoFilter ref="C3:D62" xr:uid="{AACB38A0-A41E-4166-B442-690624D094D9}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{90DF268F-7A7E-4316-84A2-C65E680CCEC3}" name="Término" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{50DFDDD4-B692-4DEE-9CB2-F6D16F5C131B}" name="Definición" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{90DF268F-7A7E-4316-84A2-C65E680CCEC3}" name="Término" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{50DFDDD4-B692-4DEE-9CB2-F6D16F5C131B}" name="Definición" dataDxfId="119"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D99A6A2B-287D-414B-97A5-BBAC531D4DC9}" name="Tabla14" displayName="Tabla14" ref="B3:B62" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D99A6A2B-287D-414B-97A5-BBAC531D4DC9}" name="Tabla14" displayName="Tabla14" ref="B3:B62" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117">
   <autoFilter ref="B3:B62" xr:uid="{D99A6A2B-287D-414B-97A5-BBAC531D4DC9}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A312D238-B542-4541-B4D7-67F50F0A3A97}" name="No." dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{A312D238-B542-4541-B4D7-67F50F0A3A97}" name="No." dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{7F6A2A40-E092-4E54-9605-F58F6C05F607}" name="Tabla15" displayName="Tabla15" ref="C65:E70" totalsRowShown="0" headerRowDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{7F6A2A40-E092-4E54-9605-F58F6C05F607}" name="Tabla15" displayName="Tabla15" ref="C65:E70" totalsRowShown="0" headerRowDxfId="115">
   <autoFilter ref="C65:E70" xr:uid="{7F6A2A40-E092-4E54-9605-F58F6C05F607}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9E7467CE-4AF4-4C96-913C-DA84BA745BD4}" name="Capa" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{7FBBB835-361D-4DCD-B48E-8D871F87C180}" name="Responsabilidad" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{8E2C3BC0-B50A-4CD3-B3B5-9FF61E432512}" name="Implementación" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{9E7467CE-4AF4-4C96-913C-DA84BA745BD4}" name="Capa" dataDxfId="114"/>
+    <tableColumn id="2" xr3:uid="{7FBBB835-361D-4DCD-B48E-8D871F87C180}" name="Responsabilidad" dataDxfId="113"/>
+    <tableColumn id="3" xr3:uid="{8E2C3BC0-B50A-4CD3-B3B5-9FF61E432512}" name="Implementación" dataDxfId="112"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B5E7B612-4CE4-45C6-9721-563B0320E830}" name="Tabla16" displayName="Tabla16" ref="C72:D80" totalsRowShown="0" headerRowDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B5E7B612-4CE4-45C6-9721-563B0320E830}" name="Tabla16" displayName="Tabla16" ref="C72:D80" totalsRowShown="0" headerRowDxfId="111">
   <autoFilter ref="C72:D80" xr:uid="{B5E7B612-4CE4-45C6-9721-563B0320E830}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{28125A43-6CD1-43EE-9B9C-BD31CB063DA8}" name="Patrón" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{98254B4C-908A-4D53-805A-AA8CCD25F617}" name="Uso concreto en el sistema" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{28125A43-6CD1-43EE-9B9C-BD31CB063DA8}" name="Patrón" dataDxfId="110"/>
+    <tableColumn id="2" xr3:uid="{98254B4C-908A-4D53-805A-AA8CCD25F617}" name="Uso concreto en el sistema" dataDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{D2FC5B83-6C3E-47C1-8865-60749636AB51}" name="Tabla17" displayName="Tabla17" ref="C83:F91" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{D2FC5B83-6C3E-47C1-8865-60749636AB51}" name="Tabla17" displayName="Tabla17" ref="C83:F91" totalsRowShown="0" headerRowDxfId="108">
   <autoFilter ref="C83:F91" xr:uid="{D2FC5B83-6C3E-47C1-8865-60749636AB51}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{47368D22-0B07-410B-989D-C744F709A87D}" name="Tecnología" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{336351F0-4A9D-4874-BC49-211670765F42}" name="Versión" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{47368D22-0B07-410B-989D-C744F709A87D}" name="Tecnología" dataDxfId="107"/>
+    <tableColumn id="2" xr3:uid="{336351F0-4A9D-4874-BC49-211670765F42}" name="Versión" dataDxfId="106"/>
     <tableColumn id="3" xr3:uid="{423F8B28-7178-4D2D-A570-380074572818}" name="Licencia"/>
     <tableColumn id="4" xr3:uid="{F4408031-D979-4027-9079-6AD65F7CAD3D}" name="Rol"/>
   </tableColumns>
@@ -6710,11 +10407,11 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C29A4340-04BD-4F8D-A065-7BEF5D96CC2A}" name="Tabla18" displayName="Tabla18" ref="C93:F96" totalsRowShown="0" headerRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{C29A4340-04BD-4F8D-A065-7BEF5D96CC2A}" name="Tabla18" displayName="Tabla18" ref="C93:F96" totalsRowShown="0" headerRowDxfId="105">
   <autoFilter ref="C93:F96" xr:uid="{C29A4340-04BD-4F8D-A065-7BEF5D96CC2A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{ED620A20-40AF-41B8-BEEC-99DF747ED1FD}" name="Tecnología" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{FF4E3891-76FF-4F70-A6ED-3C3A5C75EEE3}" name="Versión" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{ED620A20-40AF-41B8-BEEC-99DF747ED1FD}" name="Tecnología" dataDxfId="104"/>
+    <tableColumn id="2" xr3:uid="{FF4E3891-76FF-4F70-A6ED-3C3A5C75EEE3}" name="Versión" dataDxfId="103"/>
     <tableColumn id="3" xr3:uid="{D89C3FD6-72FC-4B56-807D-72FDB72A49D6}" name="Licencia"/>
     <tableColumn id="4" xr3:uid="{E12AAD54-82BC-45D5-B4BD-5E5FC01449FC}" name="Rol"/>
   </tableColumns>
@@ -6723,11 +10420,11 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{62857DFB-1AF7-4ACC-9B37-05E4DC879F32}" name="Tabla19" displayName="Tabla19" ref="C98:F103" totalsRowShown="0" headerRowDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{62857DFB-1AF7-4ACC-9B37-05E4DC879F32}" name="Tabla19" displayName="Tabla19" ref="C98:F103" totalsRowShown="0" headerRowDxfId="102">
   <autoFilter ref="C98:F103" xr:uid="{62857DFB-1AF7-4ACC-9B37-05E4DC879F32}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0638947F-FA2A-4EDD-B2FE-39510F3AD1AD}" name="Tecnología" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{12255D88-E601-4F0D-A6DF-7F75C8EBB5EB}" name="Versión" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{0638947F-FA2A-4EDD-B2FE-39510F3AD1AD}" name="Tecnología" dataDxfId="101"/>
+    <tableColumn id="2" xr3:uid="{12255D88-E601-4F0D-A6DF-7F75C8EBB5EB}" name="Versión" dataDxfId="100"/>
     <tableColumn id="3" xr3:uid="{439AC9B5-DBAF-456F-BA13-B097B7BD4F80}" name="Licencia"/>
     <tableColumn id="4" xr3:uid="{F4A8BAB4-7A56-43A9-9EF4-8C056B90C004}" name="Rol"/>
   </tableColumns>
@@ -6736,7 +10433,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E4A64FDB-1615-4C52-9695-4BF968FACE76}" name="Tabla3" displayName="Tabla3" ref="B3:E19" totalsRowShown="0" headerRowDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E4A64FDB-1615-4C52-9695-4BF968FACE76}" name="Tabla3" displayName="Tabla3" ref="B3:E19" totalsRowShown="0" headerRowDxfId="145">
   <autoFilter ref="B3:E19" xr:uid="{E4A64FDB-1615-4C52-9695-4BF968FACE76}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{27304D01-6A0F-407C-88B0-1AACB353D29B}" name="Servicio Azure"/>
@@ -6749,11 +10446,11 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{DA817B9C-8709-4397-8453-FAE4EA2CC43C}" name="Tabla20" displayName="Tabla20" ref="C105:F116" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{DA817B9C-8709-4397-8453-FAE4EA2CC43C}" name="Tabla20" displayName="Tabla20" ref="C105:F116" totalsRowShown="0" headerRowDxfId="99">
   <autoFilter ref="C105:F116" xr:uid="{DA817B9C-8709-4397-8453-FAE4EA2CC43C}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{498BBEF6-8375-41E9-9881-E434046AF5DF}" name="Tecnología" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{A6CEB9ED-A9FD-4CB6-8D34-1E66578770C1}" name="Versión" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{498BBEF6-8375-41E9-9881-E434046AF5DF}" name="Tecnología" dataDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{A6CEB9ED-A9FD-4CB6-8D34-1E66578770C1}" name="Versión" dataDxfId="97"/>
     <tableColumn id="3" xr3:uid="{6FB59665-3E02-4DF5-A847-1F048A2A190F}" name="Licencia"/>
     <tableColumn id="4" xr3:uid="{81C4D2C1-8C26-470D-869F-E8F9FE515C16}" name="Rol"/>
   </tableColumns>
@@ -6762,11 +10459,11 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{0CED1471-62F5-44E5-ACBB-AFEB36735815}" name="Tabla21" displayName="Tabla21" ref="C119:F122" totalsRowShown="0" headerRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{0CED1471-62F5-44E5-ACBB-AFEB36735815}" name="Tabla21" displayName="Tabla21" ref="C119:F122" totalsRowShown="0" headerRowDxfId="96">
   <autoFilter ref="C119:F122" xr:uid="{0CED1471-62F5-44E5-ACBB-AFEB36735815}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D72A8A91-F9A0-43B4-AF2F-69B6B828469F}" name="Tecnología" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{AA73234C-268B-403C-A281-B0DEAB0935D2}" name="Versión" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{D72A8A91-F9A0-43B4-AF2F-69B6B828469F}" name="Tecnología" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{AA73234C-268B-403C-A281-B0DEAB0935D2}" name="Versión" dataDxfId="94"/>
     <tableColumn id="3" xr3:uid="{7C3E09C3-C419-47AD-AAE8-D5C9E79156A3}" name="Licencia"/>
     <tableColumn id="4" xr3:uid="{3E162C25-8A3A-49E8-9A19-43E0B6331ECC}" name="Rol"/>
   </tableColumns>
@@ -6775,39 +10472,39 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{846502CF-6C1F-4589-911E-9AD93B415F94}" name="Tabla22" displayName="Tabla22" ref="C125:G131" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{846502CF-6C1F-4589-911E-9AD93B415F94}" name="Tabla22" displayName="Tabla22" ref="C125:G131" totalsRowShown="0" headerRowDxfId="93" dataDxfId="92">
   <autoFilter ref="C125:G131" xr:uid="{846502CF-6C1F-4589-911E-9AD93B415F94}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A5401688-0800-4A2A-82F6-87CADFD1E784}" name="Criterio" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{349DEF42-AED4-42BE-8DC1-6B0E5FCB1128}" name="NestJS ✅" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{A80D0773-1443-42C7-8688-EC589F79C4FE}" name="Express puro" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{64F97808-57F8-4436-8BC4-0EC9CA2F9B0C}" name="Fastify" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{B29EC9EC-D71D-4989-B65F-9F69DA603988}" name="Hapi" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{A5401688-0800-4A2A-82F6-87CADFD1E784}" name="Criterio" dataDxfId="91"/>
+    <tableColumn id="2" xr3:uid="{349DEF42-AED4-42BE-8DC1-6B0E5FCB1128}" name="NestJS ✅" dataDxfId="90"/>
+    <tableColumn id="3" xr3:uid="{A80D0773-1443-42C7-8688-EC589F79C4FE}" name="Express puro" dataDxfId="89"/>
+    <tableColumn id="4" xr3:uid="{64F97808-57F8-4436-8BC4-0EC9CA2F9B0C}" name="Fastify" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{B29EC9EC-D71D-4989-B65F-9F69DA603988}" name="Hapi" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{5908BC9A-AB6A-41C3-91C3-91D13BC23D00}" name="Tabla23" displayName="Tabla23" ref="C134:G139" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{5908BC9A-AB6A-41C3-91C3-91D13BC23D00}" name="Tabla23" displayName="Tabla23" ref="C134:G139" totalsRowShown="0" headerRowDxfId="86" dataDxfId="85">
   <autoFilter ref="C134:G139" xr:uid="{5908BC9A-AB6A-41C3-91C3-91D13BC23D00}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0AEF401E-57D6-448C-8BA5-9D87F9CEED0F}" name="Criterio" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{4E1B27A6-6B72-4E61-9E9B-24F4D5EFAA0F}" name="React + Vite ✅" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{4B239269-509C-42B2-A198-9927BF1FC289}" name="Angular" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{EA440BD9-4ED7-4041-A936-73D1F5F26F6E}" name="Vue 3" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{BB133910-CF69-4D99-89D1-C1877E8C7E44}" name="SvelteKit" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{0AEF401E-57D6-448C-8BA5-9D87F9CEED0F}" name="Criterio" dataDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{4E1B27A6-6B72-4E61-9E9B-24F4D5EFAA0F}" name="React + Vite ✅" dataDxfId="83"/>
+    <tableColumn id="3" xr3:uid="{4B239269-509C-42B2-A198-9927BF1FC289}" name="Angular" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{EA440BD9-4ED7-4041-A936-73D1F5F26F6E}" name="Vue 3" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{BB133910-CF69-4D99-89D1-C1877E8C7E44}" name="SvelteKit" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{83B9F76F-340F-4D62-B4F8-DF89E9E502D4}" name="Tabla24" displayName="Tabla24" ref="C141:G146" totalsRowShown="0" headerRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{83B9F76F-340F-4D62-B4F8-DF89E9E502D4}" name="Tabla24" displayName="Tabla24" ref="C141:G146" totalsRowShown="0" headerRowDxfId="79">
   <autoFilter ref="C141:G146" xr:uid="{83B9F76F-340F-4D62-B4F8-DF89E9E502D4}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{EB12EBDB-49E9-4CA1-B357-4FE08A318990}" name="Criterio" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{32CFD4FF-B833-4C33-B41B-0D68743C469F}" name="Next.js 14 SSR ✅" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{EB12EBDB-49E9-4CA1-B357-4FE08A318990}" name="Criterio" dataDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{32CFD4FF-B833-4C33-B41B-0D68743C469F}" name="Next.js 14 SSR ✅" dataDxfId="77"/>
     <tableColumn id="3" xr3:uid="{A40A1297-2C45-4A1B-97BB-B68438275280}" name="Gatsby"/>
     <tableColumn id="4" xr3:uid="{A13F817C-44A7-400D-BD2A-72221A566447}" name="Remix"/>
     <tableColumn id="5" xr3:uid="{8D59BB7F-86D4-45BB-ADC0-7DD726283BB1}" name="Astro"/>
@@ -6817,73 +10514,73 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{BF493B22-1B76-4538-BEA2-FD58E18DB6B5}" name="Tabla25" displayName="Tabla25" ref="C148:G153" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{BF493B22-1B76-4538-BEA2-FD58E18DB6B5}" name="Tabla25" displayName="Tabla25" ref="C148:G153" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
   <autoFilter ref="C148:G153" xr:uid="{BF493B22-1B76-4538-BEA2-FD58E18DB6B5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{335082A6-F1D8-40FA-A553-A4B8A539BE26}" name="Criterio" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{D1A569AE-BEF4-44E5-89F9-97984B2ACB00}" name="PostgreSQL 16 ✅" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{82CD35B9-C487-4DF4-A087-AF094C7600A7}" name="MySQL 8" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{569AF49E-7178-4326-8B70-F684D7D5755E}" name="MongoDB" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{6CDD3199-63C0-4781-A233-01F135A3B022}" name="Supabase" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{335082A6-F1D8-40FA-A553-A4B8A539BE26}" name="Criterio" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{D1A569AE-BEF4-44E5-89F9-97984B2ACB00}" name="PostgreSQL 16 ✅" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{82CD35B9-C487-4DF4-A087-AF094C7600A7}" name="MySQL 8" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{569AF49E-7178-4326-8B70-F684D7D5755E}" name="MongoDB" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{6CDD3199-63C0-4781-A233-01F135A3B022}" name="Supabase" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{B050E695-4051-4CB9-91AF-EB4D9EFAAFA1}" name="Tabla26" displayName="Tabla26" ref="B5:C15" totalsRowShown="0" headerRowDxfId="124" dataDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{B050E695-4051-4CB9-91AF-EB4D9EFAAFA1}" name="Tabla26" displayName="Tabla26" ref="B5:C15" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="B5:C15" xr:uid="{B050E695-4051-4CB9-91AF-EB4D9EFAAFA1}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B8768C81-130E-4AA8-AE9E-CA24E25E28FE}" name="Recurso" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{259A1174-63D5-44D7-9C07-94C67FB5EE2E}" name="Especificación mínima" dataDxfId="121"/>
+    <tableColumn id="1" xr3:uid="{B8768C81-130E-4AA8-AE9E-CA24E25E28FE}" name="Recurso" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{259A1174-63D5-44D7-9C07-94C67FB5EE2E}" name="Especificación mínima" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1B3F6E84-6101-42B3-B49B-9EDB988079F6}" name="Tabla27" displayName="Tabla27" ref="B18:C31" totalsRowShown="0" headerRowDxfId="120">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1B3F6E84-6101-42B3-B49B-9EDB988079F6}" name="Tabla27" displayName="Tabla27" ref="B18:C31" totalsRowShown="0" headerRowDxfId="65">
   <autoFilter ref="B18:C31" xr:uid="{1B3F6E84-6101-42B3-B49B-9EDB988079F6}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{30661648-3F68-4536-AF77-C57BBA20DB75}" name="Recurso"/>
-    <tableColumn id="2" xr3:uid="{C9EFF7A2-1F55-4CA0-A20D-EB5CFAF7CA6D}" name="Especificación recomendada" dataDxfId="119"/>
+    <tableColumn id="2" xr3:uid="{C9EFF7A2-1F55-4CA0-A20D-EB5CFAF7CA6D}" name="Especificación recomendada" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{4C022B44-987F-4693-BF43-D4E929BD1F38}" name="Tabla28" displayName="Tabla28" ref="B34:G39" totalsRowShown="0" headerRowDxfId="118">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{4C022B44-987F-4693-BF43-D4E929BD1F38}" name="Tabla28" displayName="Tabla28" ref="B34:G39" totalsRowShown="0" headerRowDxfId="63">
   <autoFilter ref="B34:G39" xr:uid="{4C022B44-987F-4693-BF43-D4E929BD1F38}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{DDA14ADC-4BD3-46BE-AC0A-738CCDB7A940}" name="ID" dataDxfId="117"/>
-    <tableColumn id="2" xr3:uid="{28443A5C-13D7-41E2-9D7B-BA788E03A2E9}" name="Modo de Fallo" dataDxfId="116"/>
-    <tableColumn id="3" xr3:uid="{0C181921-9F43-40BC-B10A-E68547A80BF9}" name="Efecto" dataDxfId="115"/>
-    <tableColumn id="4" xr3:uid="{CDBA835E-3264-4969-8805-7A95C6399CCB}" name="Prob." dataDxfId="114"/>
-    <tableColumn id="5" xr3:uid="{27905783-1C33-4232-BE7B-AC2DEC06ED37}" name="Impacto" dataDxfId="113"/>
-    <tableColumn id="6" xr3:uid="{EEF23456-87DD-4913-9B10-0A21E4B4033E}" name="Plan de Mitigación" dataDxfId="112"/>
+    <tableColumn id="1" xr3:uid="{DDA14ADC-4BD3-46BE-AC0A-738CCDB7A940}" name="ID" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{28443A5C-13D7-41E2-9D7B-BA788E03A2E9}" name="Modo de Fallo" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{0C181921-9F43-40BC-B10A-E68547A80BF9}" name="Efecto" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{CDBA835E-3264-4969-8805-7A95C6399CCB}" name="Prob." dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{27905783-1C33-4232-BE7B-AC2DEC06ED37}" name="Impacto" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{EEF23456-87DD-4913-9B10-0A21E4B4033E}" name="Plan de Mitigación" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{4AA687A6-7499-48BF-A678-5358ABBC1FB4}" name="Tabla29" displayName="Tabla29" ref="C43:H48" totalsRowShown="0" headerRowDxfId="111" dataDxfId="110">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{4AA687A6-7499-48BF-A678-5358ABBC1FB4}" name="Tabla29" displayName="Tabla29" ref="C43:H48" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="C43:H48" xr:uid="{4AA687A6-7499-48BF-A678-5358ABBC1FB4}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EE6903D4-D989-4E5F-800D-451C18E418D0}" name="Rol" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{CB5FA71C-8566-4D4E-B665-FADDB1FF0348}" name="Dedicación" dataDxfId="108"/>
-    <tableColumn id="3" xr3:uid="{170AA682-7371-4A74-81BE-F2FE57F5039C}" name="Semanas" dataDxfId="107"/>
-    <tableColumn id="4" xr3:uid="{F1C1FC94-76EE-409B-8F0E-7A4A47AF6BD3}" name="Total horas" dataDxfId="106"/>
-    <tableColumn id="5" xr3:uid="{E81AF3DE-29E7-4A3A-8A63-15DF9E27C18E}" name="Tarifa / hora (USD)" dataDxfId="105"/>
-    <tableColumn id="6" xr3:uid="{444ECB50-FD4F-4036-8B25-FDC3754A6DA9}" name="Costo total (USD)" dataDxfId="104"/>
+    <tableColumn id="1" xr3:uid="{EE6903D4-D989-4E5F-800D-451C18E418D0}" name="Rol" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{CB5FA71C-8566-4D4E-B665-FADDB1FF0348}" name="Dedicación" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{170AA682-7371-4A74-81BE-F2FE57F5039C}" name="Semanas" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{F1C1FC94-76EE-409B-8F0E-7A4A47AF6BD3}" name="Total horas" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{E81AF3DE-29E7-4A3A-8A63-15DF9E27C18E}" name="Tarifa / hora (USD)" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{444ECB50-FD4F-4036-8B25-FDC3754A6DA9}" name="Costo total (USD)" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{590442DF-90B3-490C-87FE-0DA94520885E}" name="Tabla6" displayName="Tabla6" ref="B21:D31" totalsRowShown="0" headerRowDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{590442DF-90B3-490C-87FE-0DA94520885E}" name="Tabla6" displayName="Tabla6" ref="B21:D31" totalsRowShown="0" headerRowDxfId="144">
   <autoFilter ref="B21:D31" xr:uid="{590442DF-90B3-490C-87FE-0DA94520885E}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{BAC29BA0-990C-4BC6-9C92-A78CC1C38394}" name="Servicio Azure"/>
@@ -6895,23 +10592,23 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{86540CDB-DF27-4F47-B867-0DC9235191D1}" name="Tabla30" displayName="Tabla30" ref="C51:F60" totalsRowShown="0" headerRowDxfId="103" dataDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{86540CDB-DF27-4F47-B867-0DC9235191D1}" name="Tabla30" displayName="Tabla30" ref="C51:F60" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <autoFilter ref="C51:F60" xr:uid="{86540CDB-DF27-4F47-B867-0DC9235191D1}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F08DB348-78D7-4968-904D-9D1F8E57203E}" name="Servicio GCP" dataDxfId="101"/>
-    <tableColumn id="2" xr3:uid="{9F5973AD-659E-431C-A6CC-EC1380C12FC8}" name="Producto" dataDxfId="100"/>
-    <tableColumn id="3" xr3:uid="{C97A69BF-7418-44C0-BE60-45C8E51D00DB}" name="Specs" dataDxfId="99"/>
-    <tableColumn id="4" xr3:uid="{6E790435-E2B2-42AE-9EE3-C838F6B13B3E}" name="Costo aprox./mes" dataDxfId="98"/>
+    <tableColumn id="1" xr3:uid="{F08DB348-78D7-4968-904D-9D1F8E57203E}" name="Servicio GCP" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{9F5973AD-659E-431C-A6CC-EC1380C12FC8}" name="Producto" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{C97A69BF-7418-44C0-BE60-45C8E51D00DB}" name="Specs" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{6E790435-E2B2-42AE-9EE3-C838F6B13B3E}" name="Costo aprox./mes" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{F43F5B27-E68E-4CB7-9DE5-ADD4DA87EE0D}" name="Tabla31" displayName="Tabla31" ref="C65:H66" totalsRowShown="0" headerRowDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{F43F5B27-E68E-4CB7-9DE5-ADD4DA87EE0D}" name="Tabla31" displayName="Tabla31" ref="C65:H66" totalsRowShown="0" headerRowDxfId="42">
   <autoFilter ref="C65:H66" xr:uid="{F43F5B27-E68E-4CB7-9DE5-ADD4DA87EE0D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7136A10A-BD44-4BF5-B3AE-CFA96903C33F}" name="Rubro" dataDxfId="96"/>
+    <tableColumn id="1" xr3:uid="{7136A10A-BD44-4BF5-B3AE-CFA96903C33F}" name="Rubro" dataDxfId="41"/>
     <tableColumn id="2" xr3:uid="{6C1F8937-E17F-45DC-9133-5F46335A6FD2}" name="Año 1"/>
     <tableColumn id="3" xr3:uid="{61B7AB7C-799B-4AF5-BED9-767D469C4766}" name="Año 2"/>
     <tableColumn id="4" xr3:uid="{D7AB77A6-A968-4E8B-9360-E6AAE31BDBE7}" name="Año 3"/>
@@ -6923,21 +10620,21 @@
 </file>
 
 <file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{EFBC732B-83CF-42B9-A7CC-E9B414CE3036}" name="Tabla32" displayName="Tabla32" ref="C77:D83" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{EFBC732B-83CF-42B9-A7CC-E9B414CE3036}" name="Tabla32" displayName="Tabla32" ref="C77:D83" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="C77:D83" xr:uid="{EFBC732B-83CF-42B9-A7CC-E9B414CE3036}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C2E65BBF-D25F-4055-B2F3-4266CB8094AA}" name="Elemento" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{43C97C64-FA4B-424F-98C1-3DAA5255214E}" name="Detalle" dataDxfId="92"/>
+    <tableColumn id="1" xr3:uid="{C2E65BBF-D25F-4055-B2F3-4266CB8094AA}" name="Elemento" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{43C97C64-FA4B-424F-98C1-3DAA5255214E}" name="Detalle" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{BA48AE35-3815-4CB7-A9C4-51C76633E5F1}" name="Tabla33" displayName="Tabla33" ref="C87:G106" totalsRowShown="0" headerRowDxfId="91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{BA48AE35-3815-4CB7-A9C4-51C76633E5F1}" name="Tabla33" displayName="Tabla33" ref="C87:G106" totalsRowShown="0" headerRowDxfId="36">
   <autoFilter ref="C87:G106" xr:uid="{BA48AE35-3815-4CB7-A9C4-51C76633E5F1}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D088211E-5301-41C9-9667-727F7B816CFC}" name="Funcionalidad" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{D088211E-5301-41C9-9667-727F7B816CFC}" name="Funcionalidad" dataDxfId="35"/>
     <tableColumn id="2" xr3:uid="{E2BE6EB9-B318-4EEB-AC3D-1CBCC29755F5}" name="**Free**"/>
     <tableColumn id="3" xr3:uid="{0EC3D884-2F70-41CD-8B7F-7CB4ECB3B17C}" name="**Basic**"/>
     <tableColumn id="4" xr3:uid="{4B305D05-F62B-463E-9826-D7B81C4A0563}" name="**Pro**"/>
@@ -6960,7 +10657,7 @@
 </file>
 
 <file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{AE584D6A-7942-48C5-8A3D-A1222F2E6E61}" name="Tabla35" displayName="Tabla35" ref="C116:F120" totalsRowShown="0" headerRowDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{AE584D6A-7942-48C5-8A3D-A1222F2E6E61}" name="Tabla35" displayName="Tabla35" ref="C116:F120" totalsRowShown="0" headerRowDxfId="34">
   <autoFilter ref="C116:F120" xr:uid="{AE584D6A-7942-48C5-8A3D-A1222F2E6E61}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{CD9D13C6-DCAC-4EAB-9351-6FB742A5B0DC}" name="Plan"/>
@@ -6973,7 +10670,7 @@
 </file>
 
 <file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{AA080BF9-B1F5-4631-98DB-74CFFEB23905}" name="Tabla36" displayName="Tabla36" ref="C124:D127" totalsRowShown="0" headerRowDxfId="88">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{AA080BF9-B1F5-4631-98DB-74CFFEB23905}" name="Tabla36" displayName="Tabla36" ref="C124:D127" totalsRowShown="0" headerRowDxfId="33">
   <autoFilter ref="C124:D127" xr:uid="{AA080BF9-B1F5-4631-98DB-74CFFEB23905}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{AAE66784-2D13-4F20-93B4-D2B38DFB739A}" name="Concepto"/>
@@ -6984,22 +10681,22 @@
 </file>
 
 <file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{347B5AA6-7D87-4398-81A0-5FFF76E99768}" name="Tabla37" displayName="Tabla37" ref="C129:H140" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{347B5AA6-7D87-4398-81A0-5FFF76E99768}" name="Tabla37" displayName="Tabla37" ref="C129:H140" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29">
   <autoFilter ref="C129:H140" xr:uid="{347B5AA6-7D87-4398-81A0-5FFF76E99768}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6951F522-14AC-4864-9FB1-BA3B37959629}" name="Métrica" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{0E183BD8-6354-4600-8E86-35303E6AFAE3}" name="Año 1" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{FB5F4156-47C9-41E4-9F24-5FB5B4DBAAB9}" name="Año 2" dataDxfId="81"/>
-    <tableColumn id="4" xr3:uid="{396AFB0A-7144-4BE3-B3B2-2455588C1FF9}" name="Año 3" dataDxfId="80"/>
-    <tableColumn id="5" xr3:uid="{0037FB99-6300-4504-8CAE-9870EC5C3461}" name="Año 4" dataDxfId="79"/>
-    <tableColumn id="6" xr3:uid="{7EDB12E4-AE94-4D51-8D4A-872B13200391}" name="Año 5" dataDxfId="78"/>
+    <tableColumn id="1" xr3:uid="{6951F522-14AC-4864-9FB1-BA3B37959629}" name="Métrica" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{0E183BD8-6354-4600-8E86-35303E6AFAE3}" name="Año 1" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{FB5F4156-47C9-41E4-9F24-5FB5B4DBAAB9}" name="Año 2" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{396AFB0A-7144-4BE3-B3B2-2455588C1FF9}" name="Año 3" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{0037FB99-6300-4504-8CAE-9870EC5C3461}" name="Año 4" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{7EDB12E4-AE94-4D51-8D4A-872B13200391}" name="Año 5" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{11286FF4-A02F-45D1-ABCE-805058F0DE2A}" name="Tabla39" displayName="Tabla39" ref="C145:G156" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{11286FF4-A02F-45D1-ABCE-805058F0DE2A}" name="Tabla39" displayName="Tabla39" ref="C145:G156" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="C145:G156" xr:uid="{11286FF4-A02F-45D1-ABCE-805058F0DE2A}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F1EBDDF8-3188-4532-BD40-58E8860C6181}" name="Servicio GCP"/>
@@ -7012,8 +10709,23 @@
 </table>
 </file>
 
+<file path=xl/tables/table39.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{3036BBA4-90E3-4E14-8127-87071630738D}" name="Tabla38" displayName="Tabla38" ref="C160:H162" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="C160:H162" xr:uid="{3036BBA4-90E3-4E14-8127-87071630738D}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{92DED65A-1555-4419-B1DC-B02675591B86}" name="Configuración" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{80B926BA-2793-4FF6-9730-86E9D5218FDA}" name="Costo/mes" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{A8479D4F-554A-42DA-A4E9-DF23F3E710BE}" name="Tenants (agencias)" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{836E4477-7280-4243-99D9-3E69BCCC942B}" name="Agentes concurrentes" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{4F9D2593-F20B-4DD3-8901-B71EDB53667E}" name="Propiedades activas" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{8DCCAF24-2F9E-4D4D-BCC9-044241AACD9A}" name="Tráfico portal/mes" dataDxfId="14"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3EAE41C6-2DEA-43BA-A41D-DA6CACC25005}" name="Tabla7" displayName="Tabla7" ref="B33:D45" totalsRowShown="0" headerRowDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3EAE41C6-2DEA-43BA-A41D-DA6CACC25005}" name="Tabla7" displayName="Tabla7" ref="B33:D45" totalsRowShown="0" headerRowDxfId="143">
   <autoFilter ref="B33:D45" xr:uid="{3EAE41C6-2DEA-43BA-A41D-DA6CACC25005}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7A75A639-0A77-4C54-9503-4045B9CD2387}" name="Servicio Azure"/>
@@ -7024,8 +10736,121 @@
 </table>
 </file>
 
+<file path=xl/tables/table40.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{B6DC69B3-10EC-4D35-9BDD-03DA0EC3FCCE}" name="Tabla40" displayName="Tabla40" ref="K5:M10" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="K5:M10" xr:uid="{B6DC69B3-10EC-4D35-9BDD-03DA0EC3FCCE}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{9FD8AD5A-1355-4269-9EDA-B1249E92570F}" name="Concepto" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{2353A8DD-3D29-4DEE-A3E2-03295713DD73}" name="Especificación referencial" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{FBCF0390-2B8B-49F5-B8B0-0DD88A0C7E2F}" name="Costo (USD)" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table41.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{000BC125-A545-4359-AF48-3E288A1510BC}" name="Tabla41" displayName="Tabla41" ref="B3:F8" totalsRowShown="0" headerRowDxfId="174" dataDxfId="173">
+  <autoFilter ref="B3:F8" xr:uid="{000BC125-A545-4359-AF48-3E288A1510BC}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{CC984F80-38DB-4C4D-8093-1D8E8BEF90AE}" name="Concepto" dataDxfId="172"/>
+    <tableColumn id="2" xr3:uid="{B7816BED-A2C1-45DF-9BD9-A842803023D9}" name="Plan" dataDxfId="171"/>
+    <tableColumn id="3" xr3:uid="{13BBE647-8E28-4496-989B-A695288D9E80}" name="Duración" dataDxfId="170"/>
+    <tableColumn id="4" xr3:uid="{B9F100D8-9524-40D2-BA9C-235C4C16E449}" name="Costo (USD)" dataDxfId="169"/>
+    <tableColumn id="5" xr3:uid="{5AA2BAAA-A9BF-46F2-A1D7-4BB224D8FC37}" name="Observación" dataDxfId="168"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table42.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{78D6C4CD-BBE0-4561-B426-EC1E9C20B7BB}" name="Tabla42" displayName="Tabla42" ref="B12:C17" totalsRowShown="0" headerRowDxfId="167">
+  <autoFilter ref="B12:C17" xr:uid="{78D6C4CD-BBE0-4561-B426-EC1E9C20B7BB}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{C7D46328-90B6-4528-8174-83EDD4045139}" name="Categoría"/>
+    <tableColumn id="2" xr3:uid="{9F0D0D9E-1FEF-4342-B495-8F2D7F527375}" name="Costo (USD)" dataDxfId="166"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table43.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{09CA70B2-4190-4248-996E-65A8C6929AA1}" name="Tabla43" displayName="Tabla43" ref="B21:E25" totalsRowShown="0" headerRowDxfId="165">
+  <autoFilter ref="B21:E25" xr:uid="{09CA70B2-4190-4248-996E-65A8C6929AA1}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{3B3FCFF3-4499-4C05-A22C-93970A6923BC}" name="Concepto"/>
+    <tableColumn id="2" xr3:uid="{574467B8-7111-4ABE-A78E-10E99F3E9FC1}" name="Producto GCP"/>
+    <tableColumn id="3" xr3:uid="{228CD964-C353-4312-8900-FFEDBF3FC9AF}" name="Duración"/>
+    <tableColumn id="4" xr3:uid="{93D0B7F9-8E1A-4A48-9BC2-5B98186B1B5B}" name="Costo (USD)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table44.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{1886C670-5132-4187-B166-2727D6C2B15B}" name="Tabla44" displayName="Tabla44" ref="B55:G62" totalsRowShown="0" headerRowDxfId="164" dataDxfId="163">
+  <autoFilter ref="B55:G62" xr:uid="{1886C670-5132-4187-B166-2727D6C2B15B}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{5C2BBFF0-6AD1-4E87-A794-7F46EC368F4C}" name="Rubro" dataDxfId="162"/>
+    <tableColumn id="2" xr3:uid="{3894F3F5-BEC9-4620-89E6-B0F3ACFB2D38}" name="Año 1" dataDxfId="161"/>
+    <tableColumn id="3" xr3:uid="{121E6E5F-F16C-4432-BC69-7E9D8B6D07C6}" name="Año 2" dataDxfId="160"/>
+    <tableColumn id="4" xr3:uid="{7F09B870-84E4-4DD1-AB74-94AF604305FA}" name="Año 3" dataDxfId="159"/>
+    <tableColumn id="5" xr3:uid="{F9E5C348-4C99-47FB-85FC-A9BEFEDB4996}" name="Año 4" dataDxfId="158"/>
+    <tableColumn id="6" xr3:uid="{F474DA0A-116D-47AE-A7D6-BC7F6FCEA05A}" name="Año 5" dataDxfId="157"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table45.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{C0A8F2A8-D951-43FB-B0A0-C7332A18B3CB}" name="Tabla45" displayName="Tabla45" ref="B65:H70" totalsRowShown="0" headerRowDxfId="156" dataDxfId="155">
+  <autoFilter ref="B65:H70" xr:uid="{C0A8F2A8-D951-43FB-B0A0-C7332A18B3CB}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{2124EFD1-584F-41E1-ABBA-A1613FB06CD0}" name="Concepto" dataDxfId="154"/>
+    <tableColumn id="2" xr3:uid="{781B0F6A-77E5-458D-8961-EA120BABE852}" name="Año 0" dataDxfId="153"/>
+    <tableColumn id="3" xr3:uid="{6AA5CC27-EDA7-4865-9519-79E931586FA7}" name="Año 1" dataDxfId="152"/>
+    <tableColumn id="4" xr3:uid="{E74B2AD7-B9CA-4E7D-AB54-299BF1095CE6}" name="Año 2" dataDxfId="151"/>
+    <tableColumn id="5" xr3:uid="{E14BA819-F00B-4B4B-B4A0-60D57BC154DF}" name="Año 3" dataDxfId="150"/>
+    <tableColumn id="6" xr3:uid="{121FDED8-3F67-4FF5-B166-B26E072FB2FB}" name="Año 4" dataDxfId="149"/>
+    <tableColumn id="7" xr3:uid="{64F073CB-E66E-4BA9-9373-A5FFBE936A55}" name="Año 5" dataDxfId="148"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table46.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{0F1E464E-7A91-41F5-A097-2A8E6B67293D}" name="Tabla46" displayName="Tabla46" ref="B73:H82" totalsRowShown="0" headerRowDxfId="147">
+  <autoFilter ref="B73:H82" xr:uid="{0F1E464E-7A91-41F5-A097-2A8E6B67293D}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{66142EF6-8DF6-4584-B998-EAAF8E244089}" name="Plan"/>
+    <tableColumn id="2" xr3:uid="{84068A4B-FF84-4F3C-8340-9772FD5C3F93}" name="Precio/mes"/>
+    <tableColumn id="3" xr3:uid="{F67D2EA4-FB20-47E0-A5A9-7477905355B1}" name="Año 1"/>
+    <tableColumn id="4" xr3:uid="{4BB6E292-0E35-45F5-87E3-CF3594D6EBE8}" name="Año 2"/>
+    <tableColumn id="5" xr3:uid="{A2F0626B-9AE5-4722-B679-BAF70831E5BD}" name="Año 3"/>
+    <tableColumn id="6" xr3:uid="{EA528870-AE31-4367-A421-59A5EA1AE04B}" name="Año 4"/>
+    <tableColumn id="7" xr3:uid="{CEA48ACE-8E9D-4008-B2A9-9EA5CE68CA76}" name="Año 5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="47" xr:uid="{94B79FAE-FE4F-4153-8B46-C23507E26485}" name="Tabla4548" displayName="Tabla4548" ref="B44:H49" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="B44:H49" xr:uid="{94B79FAE-FE4F-4153-8B46-C23507E26485}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{144F9F77-DDD0-41A6-B740-1EA2C3523260}" name="Concepto" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{A5290C1D-3F5D-491F-8BCA-B5626DE0C86D}" name="Año 0" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{E1710A4A-255B-4758-B9D5-D072BFDB2DBB}" name="Año 1" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{5BDFAA92-B875-4A3C-9119-CB96FC8AE0D4}" name="Año 2" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{E4763C14-0D4A-49D0-BB35-177D1EC693BB}" name="Año 3" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{C5D4880D-5F43-427E-80EA-EE5C0C134D8A}" name="Año 4" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{51981605-DE5A-40FA-9C50-515E2E865E6E}" name="Año 5" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DE0D983A-C793-453C-8D7F-708EB64394F5}" name="Tabla8" displayName="Tabla8" ref="B47:F50" totalsRowShown="0" headerRowDxfId="73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DE0D983A-C793-453C-8D7F-708EB64394F5}" name="Tabla8" displayName="Tabla8" ref="B47:F50" totalsRowShown="0" headerRowDxfId="142">
   <autoFilter ref="B47:F50" xr:uid="{DE0D983A-C793-453C-8D7F-708EB64394F5}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{3C1DD1E1-ED6A-4E8A-BB9D-1571BC9F06E2}" name="Fase"/>
@@ -7039,7 +10864,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{F3B3D904-2C4B-4F90-83EA-86F19FED0396}" name="Tabla9" displayName="Tabla9" ref="B53:E68" totalsRowShown="0" headerRowDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{F3B3D904-2C4B-4F90-83EA-86F19FED0396}" name="Tabla9" displayName="Tabla9" ref="B53:E68" totalsRowShown="0" headerRowDxfId="141">
   <autoFilter ref="B53:E68" xr:uid="{F3B3D904-2C4B-4F90-83EA-86F19FED0396}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8A8CF722-49C5-4DEA-9A05-DBBEF4BCC087}" name="Columna1"/>
@@ -7052,19 +10877,19 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07FF09FD-BD7F-43F0-9F49-CD37E1FA8C5B}" name="Tabla2" displayName="Tabla2" ref="B73:D81" totalsRowShown="0" headerRowDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07FF09FD-BD7F-43F0-9F49-CD37E1FA8C5B}" name="Tabla2" displayName="Tabla2" ref="B73:D81" totalsRowShown="0" headerRowDxfId="140">
   <autoFilter ref="B73:D81" xr:uid="{07FF09FD-BD7F-43F0-9F49-CD37E1FA8C5B}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D638FD3C-E469-4D55-B5D4-B69DE2B3948D}" name="No."/>
     <tableColumn id="2" xr3:uid="{291F7657-E73A-4955-9F61-3E9F87DCA035}" name="Stakeholder"/>
-    <tableColumn id="3" xr3:uid="{83DD990E-FC61-4DC3-9D71-549838987EFB}" name="Rol en el sistema" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{83DD990E-FC61-4DC3-9D71-549838987EFB}" name="Rol en el sistema" dataDxfId="139"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7B6C4344-CBD2-4BA2-A19C-FB3401B740EF}" name="Tabla5" displayName="Tabla5" ref="B84:K96" totalsRowShown="0" headerRowDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7B6C4344-CBD2-4BA2-A19C-FB3401B740EF}" name="Tabla5" displayName="Tabla5" ref="B84:K96" totalsRowShown="0" headerRowDxfId="138">
   <autoFilter ref="B84:K96" xr:uid="{7B6C4344-CBD2-4BA2-A19C-FB3401B740EF}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{B603B3F2-13B5-4DC0-BDF6-24054103C684}" name="No."/>
@@ -7083,14 +10908,14 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{42D50FC8-95DA-4E49-8C4E-F10E0F19DEBB}" name="Tabla10" displayName="Tabla10" ref="C100:G108" totalsRowShown="0" headerRowDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{42D50FC8-95DA-4E49-8C4E-F10E0F19DEBB}" name="Tabla10" displayName="Tabla10" ref="C100:G108" totalsRowShown="0" headerRowDxfId="137">
   <autoFilter ref="C100:G108" xr:uid="{42D50FC8-95DA-4E49-8C4E-F10E0F19DEBB}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{592E1503-4578-434E-A32E-186BEB99B52B}" name="Stakeholder"/>
     <tableColumn id="2" xr3:uid="{9851230C-50F5-47D3-9F43-AA23F5634B63}" name="Poder"/>
     <tableColumn id="3" xr3:uid="{A171360C-5A07-4D31-9284-65BD59487EED}" name="Interés"/>
     <tableColumn id="4" xr3:uid="{8CE05DFC-4357-49CA-896C-03C64492D09D}" name="Cuadrante"/>
-    <tableColumn id="5" xr3:uid="{A0D9DA89-C61A-434C-9AAF-72025E3284C4}" name="Estrategia" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{A0D9DA89-C61A-434C-9AAF-72025E3284C4}" name="Estrategia" dataDxfId="136"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7390,16 +11215,16 @@
       <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -7420,10 +11245,10 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="55" t="s">
+      <c r="L5" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="55"/>
+      <c r="M5" s="56"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
@@ -7575,7 +11400,7 @@
       <c r="F11" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="55" t="s">
+      <c r="I11" s="56" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="4"/>
@@ -7584,7 +11409,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="55" t="s">
+      <c r="P11" s="56" t="s">
         <v>24</v>
       </c>
     </row>
@@ -7604,14 +11429,14 @@
       <c r="F12" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="55"/>
+      <c r="I12" s="56"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
-      <c r="P12" s="55"/>
+      <c r="P12" s="56"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
@@ -7729,10 +11554,10 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
-      <c r="L18" s="55" t="s">
+      <c r="L18" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="55"/>
+      <c r="M18" s="56"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
@@ -7745,6 +11570,877 @@
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="L18:M18"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73BC469-4D93-40AE-9AB0-6C18BC6390FC}">
+  <dimension ref="B2:X21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="64"/>
+    <col min="2" max="2" width="0.33203125" style="64" customWidth="1"/>
+    <col min="3" max="3" width="1.77734375" style="64" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" style="65" customWidth="1"/>
+    <col min="5" max="5" width="1.77734375" style="64" customWidth="1"/>
+    <col min="6" max="6" width="0.33203125" style="64" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="64" customWidth="1"/>
+    <col min="8" max="8" width="0.33203125" style="64" customWidth="1"/>
+    <col min="9" max="9" width="1.77734375" style="64" customWidth="1"/>
+    <col min="10" max="10" width="20.77734375" style="64" customWidth="1"/>
+    <col min="11" max="11" width="1.77734375" style="64" customWidth="1"/>
+    <col min="12" max="12" width="0.33203125" style="64" customWidth="1"/>
+    <col min="13" max="13" width="3.77734375" style="64" customWidth="1"/>
+    <col min="14" max="14" width="0.33203125" style="64" customWidth="1"/>
+    <col min="15" max="15" width="1.77734375" style="64" customWidth="1"/>
+    <col min="16" max="16" width="20.77734375" style="64" customWidth="1"/>
+    <col min="17" max="17" width="1.77734375" style="64" customWidth="1"/>
+    <col min="18" max="18" width="0.33203125" style="64" customWidth="1"/>
+    <col min="19" max="19" width="3.77734375" style="64" customWidth="1"/>
+    <col min="20" max="20" width="0.33203125" style="64" customWidth="1"/>
+    <col min="21" max="21" width="1.77734375" style="64" customWidth="1"/>
+    <col min="22" max="22" width="20.77734375" style="64" customWidth="1"/>
+    <col min="23" max="23" width="1.77734375" style="64" customWidth="1"/>
+    <col min="24" max="24" width="0.33203125" style="64" customWidth="1"/>
+    <col min="25" max="16384" width="11.5546875" style="64"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:24" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J2" s="64" t="s">
+        <v>662</v>
+      </c>
+      <c r="P2" s="64" t="s">
+        <v>1441</v>
+      </c>
+      <c r="V2" s="64" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24" ht="1.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="113"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="116"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="116"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="109"/>
+      <c r="R3" s="116"/>
+      <c r="T3" s="113"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="109"/>
+      <c r="W3" s="109"/>
+      <c r="X3" s="116"/>
+    </row>
+    <row r="4" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="114"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="117"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="117"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="100"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="117"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="86"/>
+      <c r="V4" s="87"/>
+      <c r="W4" s="88"/>
+      <c r="X4" s="117"/>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B5" s="114"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="84" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E5" s="79"/>
+      <c r="F5" s="117"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="90" t="s">
+        <v>662</v>
+      </c>
+      <c r="K5" s="71"/>
+      <c r="L5" s="117"/>
+      <c r="N5" s="114"/>
+      <c r="O5" s="102"/>
+      <c r="P5" s="90" t="s">
+        <v>1441</v>
+      </c>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="117"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="97" t="s">
+        <v>1442</v>
+      </c>
+      <c r="W5" s="91"/>
+      <c r="X5" s="117"/>
+    </row>
+    <row r="6" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="114"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="117"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="117"/>
+      <c r="N6" s="114"/>
+      <c r="O6" s="102"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="117"/>
+      <c r="T6" s="114"/>
+      <c r="U6" s="89"/>
+      <c r="V6" s="94"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="117"/>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B7" s="114"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="80" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E7" s="79"/>
+      <c r="F7" s="117"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="66" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K7" s="71"/>
+      <c r="L7" s="117"/>
+      <c r="N7" s="114"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="105" t="s">
+        <v>1656</v>
+      </c>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="117"/>
+      <c r="T7" s="114"/>
+      <c r="U7" s="89"/>
+      <c r="V7" s="92" t="s">
+        <v>1658</v>
+      </c>
+      <c r="W7" s="91"/>
+      <c r="X7" s="117"/>
+    </row>
+    <row r="8" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="114"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="117"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="117"/>
+      <c r="N8" s="114"/>
+      <c r="O8" s="102"/>
+      <c r="P8" s="106"/>
+      <c r="Q8" s="103"/>
+      <c r="R8" s="117"/>
+      <c r="T8" s="114"/>
+      <c r="U8" s="89"/>
+      <c r="V8" s="93"/>
+      <c r="W8" s="91"/>
+      <c r="X8" s="117"/>
+    </row>
+    <row r="9" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="114"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="117"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="117"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="102"/>
+      <c r="P9" s="104"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="117"/>
+      <c r="T9" s="114"/>
+      <c r="U9" s="89"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="91"/>
+      <c r="X9" s="117"/>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B10" s="114"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="85" t="s">
+        <v>1687</v>
+      </c>
+      <c r="E10" s="79"/>
+      <c r="F10" s="117"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="98" t="s">
+        <v>1690</v>
+      </c>
+      <c r="K10" s="71"/>
+      <c r="L10" s="117"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="104" t="s">
+        <v>1692</v>
+      </c>
+      <c r="Q10" s="103"/>
+      <c r="R10" s="117"/>
+      <c r="T10" s="114"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="94" t="s">
+        <v>1694</v>
+      </c>
+      <c r="W10" s="91"/>
+      <c r="X10" s="117"/>
+    </row>
+    <row r="11" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="114"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="117"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="117"/>
+      <c r="N11" s="114"/>
+      <c r="O11" s="102"/>
+      <c r="P11" s="104"/>
+      <c r="Q11" s="103"/>
+      <c r="R11" s="117"/>
+      <c r="T11" s="114"/>
+      <c r="U11" s="89"/>
+      <c r="V11" s="94"/>
+      <c r="W11" s="91"/>
+      <c r="X11" s="117"/>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B12" s="114"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="85" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E12" s="79"/>
+      <c r="F12" s="117"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="98" t="s">
+        <v>1691</v>
+      </c>
+      <c r="K12" s="71"/>
+      <c r="L12" s="117"/>
+      <c r="N12" s="114"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="104" t="s">
+        <v>1693</v>
+      </c>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="117"/>
+      <c r="T12" s="114"/>
+      <c r="U12" s="89"/>
+      <c r="V12" s="94" t="s">
+        <v>1695</v>
+      </c>
+      <c r="W12" s="91"/>
+      <c r="X12" s="117"/>
+    </row>
+    <row r="13" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="114"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="117"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="117"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="102"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="103"/>
+      <c r="R13" s="117"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="89"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="91"/>
+      <c r="X13" s="117"/>
+    </row>
+    <row r="14" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="114"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="117"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="98" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K14" s="71"/>
+      <c r="L14" s="117"/>
+      <c r="N14" s="114"/>
+      <c r="O14" s="102"/>
+      <c r="P14" s="104" t="s">
+        <v>1689</v>
+      </c>
+      <c r="Q14" s="103"/>
+      <c r="R14" s="117"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="89"/>
+      <c r="V14" s="122" t="s">
+        <v>1698</v>
+      </c>
+      <c r="W14" s="91"/>
+      <c r="X14" s="117"/>
+    </row>
+    <row r="15" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="114"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="117"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="98"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="117"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="102"/>
+      <c r="P15" s="104"/>
+      <c r="Q15" s="103"/>
+      <c r="R15" s="117"/>
+      <c r="T15" s="114"/>
+      <c r="U15" s="89"/>
+      <c r="V15" s="122"/>
+      <c r="W15" s="91"/>
+      <c r="X15" s="117"/>
+    </row>
+    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B16" s="114"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="117"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="117"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="102"/>
+      <c r="P16" s="104" t="s">
+        <v>1696</v>
+      </c>
+      <c r="Q16" s="103"/>
+      <c r="R16" s="117"/>
+      <c r="T16" s="114"/>
+      <c r="U16" s="89"/>
+      <c r="V16" s="122"/>
+      <c r="W16" s="91"/>
+      <c r="X16" s="117"/>
+    </row>
+    <row r="17" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="114"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="117"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="117"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="102"/>
+      <c r="P17" s="104"/>
+      <c r="Q17" s="103"/>
+      <c r="R17" s="117"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="91"/>
+      <c r="X17" s="117"/>
+    </row>
+    <row r="18" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="114"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="117"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="117"/>
+      <c r="N18" s="114"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="104" t="s">
+        <v>1697</v>
+      </c>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="117"/>
+      <c r="T18" s="114"/>
+      <c r="U18" s="89"/>
+      <c r="V18" s="122" t="s">
+        <v>1699</v>
+      </c>
+      <c r="W18" s="91"/>
+      <c r="X18" s="117"/>
+    </row>
+    <row r="19" spans="2:24" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="114"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="117"/>
+      <c r="H19" s="114"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="117"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="104"/>
+      <c r="Q19" s="103"/>
+      <c r="R19" s="117"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="122"/>
+      <c r="W19" s="91"/>
+      <c r="X19" s="117"/>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B20" s="114"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="117"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="117"/>
+      <c r="N20" s="114"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="108"/>
+      <c r="R20" s="117"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="95"/>
+      <c r="V20" s="123"/>
+      <c r="W20" s="96"/>
+      <c r="X20" s="117"/>
+    </row>
+    <row r="21" spans="2:24" ht="1.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="115"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="118"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="118"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="118"/>
+      <c r="T21" s="115"/>
+      <c r="U21" s="111"/>
+      <c r="V21" s="111"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="118"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="V14:V16"/>
+    <mergeCell ref="V18:V20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA4B3B99-B1CD-4BE7-A307-D9521D05B2EF}">
+  <dimension ref="B3:H68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C3">
+        <v>20570</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C4">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C5">
+        <f>9600-C4</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="28" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B45" s="27" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="H45" s="27" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="27" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F46" s="27" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G46" s="27" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H46" s="27" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B47" s="27" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F47" s="27" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G47" s="27" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H47" s="27" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="27" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F48" s="27" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G48" s="27" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H48" s="27" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B49" s="27" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F49" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G49" s="27" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H49" s="27" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C54">
+        <v>20.57</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C55">
+        <v>30.172999999999998</v>
+      </c>
+      <c r="D55">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C56">
+        <v>39.886000000000003</v>
+      </c>
+      <c r="D56">
+        <v>28.571999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C57">
+        <v>49.83</v>
+      </c>
+      <c r="D57">
+        <v>65.171999999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C58">
+        <v>60.302</v>
+      </c>
+      <c r="D58">
+        <v>118.74</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C59">
+        <v>70.971999999999994</v>
+      </c>
+      <c r="D59">
+        <v>189.44399999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C62" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1706</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C63">
+        <v>20570</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>20570</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C64">
+        <v>9603</v>
+      </c>
+      <c r="D64">
+        <v>7860</v>
+      </c>
+      <c r="F64">
+        <v>30173</v>
+      </c>
+      <c r="G64">
+        <v>7860</v>
+      </c>
+    </row>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C65">
+        <v>9713</v>
+      </c>
+      <c r="D65">
+        <v>20712</v>
+      </c>
+      <c r="F65">
+        <v>39886</v>
+      </c>
+      <c r="G65">
+        <v>28572</v>
+      </c>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C66">
+        <v>9944</v>
+      </c>
+      <c r="D66">
+        <v>36600</v>
+      </c>
+      <c r="F66">
+        <v>49830</v>
+      </c>
+      <c r="G66">
+        <v>65172</v>
+      </c>
+    </row>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C67">
+        <v>10472</v>
+      </c>
+      <c r="D67">
+        <v>53568</v>
+      </c>
+      <c r="F67">
+        <v>60302</v>
+      </c>
+      <c r="G67">
+        <v>118740</v>
+      </c>
+    </row>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C68">
+        <v>10670</v>
+      </c>
+      <c r="D68">
+        <v>70704</v>
+      </c>
+      <c r="F68">
+        <v>70972</v>
+      </c>
+      <c r="G68">
+        <v>189444</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
@@ -7803,10 +12499,10 @@
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="57"/>
+      <c r="C8" s="58"/>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="12" t="s">
@@ -7881,10 +12577,10 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="57"/>
+      <c r="C20" s="58"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
@@ -7959,10 +12655,10 @@
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="57"/>
+      <c r="C32" s="58"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
@@ -8037,10 +12733,10 @@
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B44" s="56" t="s">
+      <c r="B44" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C44" s="57"/>
+      <c r="C44" s="58"/>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" s="11" t="s">
@@ -8115,10 +12811,10 @@
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B56" s="56" t="s">
+      <c r="B56" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C56" s="57"/>
+      <c r="C56" s="58"/>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" s="11" t="s">
@@ -8193,10 +12889,10 @@
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B68" s="56" t="s">
+      <c r="B68" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C68" s="57"/>
+      <c r="C68" s="58"/>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B69" s="11" t="s">
@@ -8271,10 +12967,10 @@
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B80" s="56" t="s">
+      <c r="B80" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C80" s="57"/>
+      <c r="C80" s="58"/>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" s="11" t="s">
@@ -8349,10 +13045,10 @@
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B92" s="56" t="s">
+      <c r="B92" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C92" s="57"/>
+      <c r="C92" s="58"/>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" s="11" t="s">
@@ -8427,10 +13123,10 @@
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B104" s="56" t="s">
+      <c r="B104" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C104" s="57"/>
+      <c r="C104" s="58"/>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" s="11" t="s">
@@ -8505,10 +13201,10 @@
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B116" s="56" t="s">
+      <c r="B116" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C116" s="57"/>
+      <c r="C116" s="58"/>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B117" s="11" t="s">
@@ -8583,10 +13279,10 @@
       </c>
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B128" s="56" t="s">
+      <c r="B128" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C128" s="57"/>
+      <c r="C128" s="58"/>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B129" s="11" t="s">
@@ -8661,10 +13357,10 @@
       </c>
     </row>
     <row r="140" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B140" s="56" t="s">
+      <c r="B140" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C140" s="57"/>
+      <c r="C140" s="58"/>
     </row>
     <row r="141" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B141" s="11" t="s">
@@ -8739,10 +13435,10 @@
       </c>
     </row>
     <row r="152" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B152" s="56" t="s">
+      <c r="B152" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C152" s="57"/>
+      <c r="C152" s="58"/>
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B153" s="11" t="s">
@@ -8817,10 +13513,10 @@
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B164" s="56" t="s">
+      <c r="B164" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C164" s="57"/>
+      <c r="C164" s="58"/>
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B165" s="11" t="s">
@@ -8895,10 +13591,10 @@
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B176" s="56" t="s">
+      <c r="B176" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C176" s="57"/>
+      <c r="C176" s="58"/>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B177" s="11" t="s">
@@ -8973,10 +13669,10 @@
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B188" s="56" t="s">
+      <c r="B188" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C188" s="57"/>
+      <c r="C188" s="58"/>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B189" s="11" t="s">
@@ -9051,10 +13747,10 @@
       </c>
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B200" s="56" t="s">
+      <c r="B200" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C200" s="57"/>
+      <c r="C200" s="58"/>
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B201" s="11" t="s">
@@ -9129,10 +13825,10 @@
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B212" s="56" t="s">
+      <c r="B212" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C212" s="57"/>
+      <c r="C212" s="58"/>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B213" s="11" t="s">
@@ -9207,10 +13903,10 @@
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B224" s="56" t="s">
+      <c r="B224" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C224" s="57"/>
+      <c r="C224" s="58"/>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B225" s="11" t="s">
@@ -9285,10 +13981,10 @@
       </c>
     </row>
     <row r="236" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B236" s="56" t="s">
+      <c r="B236" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C236" s="57"/>
+      <c r="C236" s="58"/>
     </row>
     <row r="237" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B237" s="11" t="s">
@@ -9363,10 +14059,10 @@
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B248" s="56" t="s">
+      <c r="B248" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C248" s="57"/>
+      <c r="C248" s="58"/>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B249" s="11" t="s">
@@ -9441,10 +14137,10 @@
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B260" s="56" t="s">
+      <c r="B260" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C260" s="57"/>
+      <c r="C260" s="58"/>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B261" s="11" t="s">
@@ -9519,10 +14215,10 @@
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B272" s="56" t="s">
+      <c r="B272" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C272" s="57"/>
+      <c r="C272" s="58"/>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B273" s="11" t="s">
@@ -9597,10 +14293,10 @@
       </c>
     </row>
     <row r="284" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B284" s="56" t="s">
+      <c r="B284" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C284" s="57"/>
+      <c r="C284" s="58"/>
     </row>
     <row r="285" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B285" s="11" t="s">
@@ -9721,10 +14417,10 @@
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="60"/>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
@@ -9743,10 +14439,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="C11" s="59"/>
+      <c r="C11" s="60"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
@@ -9821,10 +14517,10 @@
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="59" t="s">
         <v>237</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="60"/>
     </row>
     <row r="22" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B22" s="11" t="s">
@@ -9843,10 +14539,10 @@
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="59" t="s">
         <v>238</v>
       </c>
-      <c r="C24" s="59"/>
+      <c r="C24" s="60"/>
     </row>
     <row r="25" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
@@ -9865,10 +14561,10 @@
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="C27" s="59"/>
+      <c r="C27" s="60"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="11" t="s">
@@ -9979,10 +14675,10 @@
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B44" s="58" t="s">
+      <c r="B44" s="59" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="59"/>
+      <c r="C44" s="60"/>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" s="11" t="s">
@@ -10049,10 +14745,10 @@
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B53" s="58" t="s">
+      <c r="B53" s="59" t="s">
         <v>242</v>
       </c>
-      <c r="C53" s="59"/>
+      <c r="C53" s="60"/>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B54" s="11" t="s">
@@ -10095,10 +14791,10 @@
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B59" s="58" t="s">
+      <c r="B59" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="C59" s="59"/>
+      <c r="C59" s="60"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B60" s="11" t="s">
@@ -10157,10 +14853,10 @@
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B67" s="58" t="s">
+      <c r="B67" s="59" t="s">
         <v>244</v>
       </c>
-      <c r="C67" s="59"/>
+      <c r="C67" s="60"/>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B68" s="11" t="s">
@@ -10211,10 +14907,10 @@
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B74" s="58" t="s">
+      <c r="B74" s="59" t="s">
         <v>238</v>
       </c>
-      <c r="C74" s="59"/>
+      <c r="C74" s="60"/>
     </row>
     <row r="75" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B75" s="11" t="s">
@@ -10233,10 +14929,10 @@
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B77" s="58" t="s">
+      <c r="B77" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="C77" s="59"/>
+      <c r="C77" s="60"/>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B78" s="11" t="s">
@@ -10309,10 +15005,10 @@
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B89" s="58" t="s">
+      <c r="B89" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="C89" s="59"/>
+      <c r="C89" s="60"/>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B90" s="11" t="s">
@@ -10347,10 +15043,10 @@
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B94" s="58" t="s">
+      <c r="B94" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="C94" s="59"/>
+      <c r="C94" s="60"/>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" s="11" t="s">
@@ -10449,10 +15145,10 @@
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B107" s="58" t="s">
+      <c r="B107" s="59" t="s">
         <v>237</v>
       </c>
-      <c r="C107" s="59"/>
+      <c r="C107" s="60"/>
     </row>
     <row r="108" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B108" s="11" t="s">
@@ -10471,10 +15167,10 @@
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B110" s="58" t="s">
+      <c r="B110" s="59" t="s">
         <v>238</v>
       </c>
-      <c r="C110" s="59"/>
+      <c r="C110" s="60"/>
     </row>
     <row r="111" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B111" s="11" t="s">
@@ -10493,10 +15189,10 @@
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B113" s="58" t="s">
+      <c r="B113" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="C113" s="59"/>
+      <c r="C113" s="60"/>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" s="11" t="s">
@@ -10539,10 +15235,10 @@
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B119" s="58" t="s">
+      <c r="B119" s="59" t="s">
         <v>240</v>
       </c>
-      <c r="C119" s="59"/>
+      <c r="C119" s="60"/>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B120" s="11" t="s">
@@ -10615,10 +15311,10 @@
       </c>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B131" s="60" t="s">
+      <c r="B131" s="61" t="s">
         <v>235</v>
       </c>
-      <c r="C131" s="61"/>
+      <c r="C131" s="62"/>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B132" s="11" t="s">
@@ -10653,10 +15349,10 @@
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B136" s="60" t="s">
+      <c r="B136" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="C136" s="61"/>
+      <c r="C136" s="62"/>
     </row>
     <row r="137" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B137" s="11" t="s">
@@ -10747,10 +15443,10 @@
       </c>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B148" s="60" t="s">
+      <c r="B148" s="61" t="s">
         <v>237</v>
       </c>
-      <c r="C148" s="61"/>
+      <c r="C148" s="62"/>
     </row>
     <row r="149" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B149" s="11" t="s">
@@ -10769,10 +15465,10 @@
       </c>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B151" s="60" t="s">
+      <c r="B151" s="61" t="s">
         <v>238</v>
       </c>
-      <c r="C151" s="61"/>
+      <c r="C151" s="62"/>
     </row>
     <row r="152" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B152" s="11" t="s">
@@ -10791,10 +15487,10 @@
       </c>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B154" s="60" t="s">
+      <c r="B154" s="61" t="s">
         <v>239</v>
       </c>
-      <c r="C154" s="61"/>
+      <c r="C154" s="62"/>
     </row>
     <row r="155" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B155" s="11" t="s">
@@ -10845,10 +15541,10 @@
       </c>
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B161" s="60" t="s">
+      <c r="B161" s="61" t="s">
         <v>240</v>
       </c>
-      <c r="C161" s="61"/>
+      <c r="C161" s="62"/>
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B162" s="11" t="s">
@@ -10921,10 +15617,10 @@
       </c>
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B173" s="58" t="s">
+      <c r="B173" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="C173" s="59"/>
+      <c r="C173" s="60"/>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B174" s="11" t="s">
@@ -10951,10 +15647,10 @@
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B177" s="58" t="s">
+      <c r="B177" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="C177" s="59"/>
+      <c r="C177" s="60"/>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B178" s="11" t="s">
@@ -11037,10 +15733,10 @@
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B188" s="58" t="s">
+      <c r="B188" s="59" t="s">
         <v>237</v>
       </c>
-      <c r="C188" s="59"/>
+      <c r="C188" s="60"/>
     </row>
     <row r="189" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B189" s="11" t="s">
@@ -11059,10 +15755,10 @@
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B191" s="58" t="s">
+      <c r="B191" s="59" t="s">
         <v>238</v>
       </c>
-      <c r="C191" s="59"/>
+      <c r="C191" s="60"/>
     </row>
     <row r="192" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B192" s="11" t="s">
@@ -11081,10 +15777,10 @@
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B194" s="58" t="s">
+      <c r="B194" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="C194" s="59"/>
+      <c r="C194" s="60"/>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B195" s="11" t="s">
@@ -11157,10 +15853,10 @@
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B206" s="58" t="s">
+      <c r="B206" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="C206" s="59"/>
+      <c r="C206" s="60"/>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B207" s="11" t="s">
@@ -11179,10 +15875,10 @@
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B209" s="58" t="s">
+      <c r="B209" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="C209" s="59"/>
+      <c r="C209" s="60"/>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B210" s="11" t="s">
@@ -11281,10 +15977,10 @@
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B222" s="58" t="s">
+      <c r="B222" s="59" t="s">
         <v>237</v>
       </c>
-      <c r="C222" s="59"/>
+      <c r="C222" s="60"/>
     </row>
     <row r="223" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B223" s="11" t="s">
@@ -11303,10 +15999,10 @@
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B225" s="58" t="s">
+      <c r="B225" s="59" t="s">
         <v>238</v>
       </c>
-      <c r="C225" s="59"/>
+      <c r="C225" s="60"/>
     </row>
     <row r="226" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B226" s="11" t="s">
@@ -11325,10 +16021,10 @@
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B228" s="58" t="s">
+      <c r="B228" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="C228" s="59"/>
+      <c r="C228" s="60"/>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B229" s="11" t="s">
@@ -11371,10 +16067,10 @@
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B234" s="58" t="s">
+      <c r="B234" s="59" t="s">
         <v>240</v>
       </c>
-      <c r="C234" s="59"/>
+      <c r="C234" s="60"/>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B235" s="11" t="s">
@@ -11467,7 +16163,7 @@
       </c>
     </row>
     <row r="5" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="63" t="s">
         <v>459</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -11481,7 +16177,7 @@
       </c>
     </row>
     <row r="6" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="62"/>
+      <c r="B6" s="63"/>
       <c r="C6" s="17" t="s">
         <v>463</v>
       </c>
@@ -11493,7 +16189,7 @@
       </c>
     </row>
     <row r="7" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="62"/>
+      <c r="B7" s="63"/>
       <c r="C7" s="17" t="s">
         <v>466</v>
       </c>
@@ -11505,7 +16201,7 @@
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="62"/>
+      <c r="B8" s="63"/>
       <c r="C8" s="17" t="s">
         <v>469</v>
       </c>
@@ -11517,7 +16213,7 @@
       </c>
     </row>
     <row r="9" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="63" t="s">
         <v>472</v>
       </c>
       <c r="C9" s="17" t="s">
@@ -11531,7 +16227,7 @@
       </c>
     </row>
     <row r="10" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="62"/>
+      <c r="B10" s="63"/>
       <c r="C10" s="17" t="s">
         <v>476</v>
       </c>
@@ -11543,7 +16239,7 @@
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="62"/>
+      <c r="B11" s="63"/>
       <c r="C11" s="17" t="s">
         <v>479</v>
       </c>
@@ -11555,7 +16251,7 @@
       </c>
     </row>
     <row r="12" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="62"/>
+      <c r="B12" s="63"/>
       <c r="C12" s="17" t="s">
         <v>482</v>
       </c>
@@ -11567,7 +16263,7 @@
       </c>
     </row>
     <row r="13" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="62"/>
+      <c r="B13" s="63"/>
       <c r="C13" s="17" t="s">
         <v>485</v>
       </c>
@@ -11579,7 +16275,7 @@
       </c>
     </row>
     <row r="14" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="63" t="s">
         <v>488</v>
       </c>
       <c r="C14" s="17" t="s">
@@ -11593,7 +16289,7 @@
       </c>
     </row>
     <row r="15" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="62"/>
+      <c r="B15" s="63"/>
       <c r="C15" s="17" t="s">
         <v>492</v>
       </c>
@@ -11605,7 +16301,7 @@
       </c>
     </row>
     <row r="16" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="62"/>
+      <c r="B16" s="63"/>
       <c r="C16" s="17" t="s">
         <v>495</v>
       </c>
@@ -11617,7 +16313,7 @@
       </c>
     </row>
     <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="63" t="s">
         <v>498</v>
       </c>
       <c r="C17" s="17" t="s">
@@ -11631,7 +16327,7 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="62"/>
+      <c r="B18" s="63"/>
       <c r="C18" s="17" t="s">
         <v>502</v>
       </c>
@@ -11643,7 +16339,7 @@
       </c>
     </row>
     <row r="19" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B19" s="62"/>
+      <c r="B19" s="63"/>
       <c r="C19" s="17" t="s">
         <v>505</v>
       </c>
@@ -14620,7 +19316,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="60" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B60" s="31">
         <v>57</v>
       </c>
@@ -14631,7 +19327,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="61" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B61" s="31">
         <v>58</v>
       </c>
@@ -14708,7 +19404,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="70" spans="3:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C70" s="30" t="s">
         <v>998</v>
       </c>
@@ -14735,7 +19431,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="74" spans="3:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C74" s="30" t="s">
         <v>1005</v>
       </c>
@@ -16375,79 +21071,134 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A1410A-2DD1-4213-93B2-7BA26A509258}">
-  <dimension ref="B3:H156"/>
+  <dimension ref="B3:M162"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="29.21875" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" customWidth="1"/>
+    <col min="12" max="12" width="43.77734375" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" ht="216" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" ht="216" x14ac:dyDescent="0.3">
       <c r="B3" s="33" t="s">
         <v>1215</v>
       </c>
       <c r="C3" s="33"/>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="33" t="s">
         <v>1216</v>
       </c>
       <c r="C4" s="33"/>
     </row>
-    <row r="5" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="40" t="s">
         <v>1217</v>
       </c>
       <c r="C5" s="40" t="s">
         <v>1218</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="K5" s="29" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>1549</v>
+      </c>
+      <c r="M5" s="29" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="33" t="s">
         <v>1219</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>1220</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="K6" s="27" t="s">
+        <v>1552</v>
+      </c>
+      <c r="L6" s="27" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M6" s="27" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="33" t="s">
         <v>1221</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>1222</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="K7" s="27" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>1556</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="33" t="s">
         <v>1223</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="K8" s="27" t="s">
+        <v>1557</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>1558</v>
+      </c>
+      <c r="M8" s="27" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
         <v>1225</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>1226</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="K9" s="27" t="s">
+        <v>1560</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>1561</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
         <v>1227</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>1228</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="K10" s="27" t="s">
+        <v>1563</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B11" s="33" t="s">
         <v>1229</v>
       </c>
@@ -16455,7 +21206,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>1231</v>
       </c>
@@ -16463,7 +21214,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
         <v>1098</v>
       </c>
@@ -16471,7 +21222,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
         <v>1101</v>
       </c>
@@ -16479,7 +21230,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B15" s="33" t="s">
         <v>1235</v>
       </c>
@@ -16511,7 +21262,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>1240</v>
       </c>
@@ -16519,7 +21270,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" ht="72" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>1242</v>
       </c>
@@ -16559,7 +21310,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>1098</v>
       </c>
@@ -16567,7 +21318,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>1101</v>
       </c>
@@ -16583,7 +21334,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>1248</v>
       </c>
@@ -16591,7 +21342,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>1250</v>
       </c>
@@ -16699,7 +21450,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B39" s="26" t="s">
         <v>1280</v>
       </c>
@@ -16739,7 +21490,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C44" s="27" t="s">
         <v>1286</v>
       </c>
@@ -16759,7 +21510,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C45" s="27" t="s">
         <v>1291</v>
       </c>
@@ -16805,7 +21556,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C48" s="27" t="s">
         <v>1301</v>
       </c>
@@ -16817,7 +21568,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C51" s="28" t="s">
         <v>1303</v>
       </c>
@@ -16831,7 +21582,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C52" s="27" t="s">
         <v>1307</v>
       </c>
@@ -16859,7 +21610,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:6" ht="72" x14ac:dyDescent="0.3">
       <c r="C54" s="27" t="s">
         <v>1311</v>
       </c>
@@ -16887,7 +21638,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C56" s="27" t="s">
         <v>1322</v>
       </c>
@@ -16901,7 +21652,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C57" s="27" t="s">
         <v>1326</v>
       </c>
@@ -16973,7 +21724,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="66" spans="3:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
         <v>1342</v>
       </c>
@@ -17141,7 +21892,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="78" spans="3:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
         <v>1379</v>
       </c>
@@ -17157,7 +21908,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="80" spans="3:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C80" s="1" t="s">
         <v>1383</v>
       </c>
@@ -17165,7 +21916,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="81" spans="3:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:7" ht="72" x14ac:dyDescent="0.3">
       <c r="C81" s="1" t="s">
         <v>1385</v>
       </c>
@@ -17173,7 +21924,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="82" spans="3:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C82" s="1" t="s">
         <v>1387</v>
       </c>
@@ -17181,7 +21932,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="83" spans="3:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C83" s="1" t="s">
         <v>1389</v>
       </c>
@@ -17206,7 +21957,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C88" s="27" t="s">
         <v>1396</v>
       </c>
@@ -17223,7 +21974,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C89" s="27" t="s">
         <v>1399</v>
       </c>
@@ -17240,7 +21991,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C90" s="27" t="s">
         <v>1404</v>
       </c>
@@ -17274,7 +22025,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C92" s="27" t="s">
         <v>645</v>
       </c>
@@ -17291,7 +22042,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C93" s="27" t="s">
         <v>649</v>
       </c>
@@ -17308,7 +22059,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C94" s="27" t="s">
         <v>1410</v>
       </c>
@@ -17325,7 +22076,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C95" s="27" t="s">
         <v>1411</v>
       </c>
@@ -17359,7 +22110,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C97" s="27" t="s">
         <v>1413</v>
       </c>
@@ -17376,7 +22127,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C98" s="27" t="s">
         <v>1414</v>
       </c>
@@ -17393,7 +22144,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C99" s="27" t="s">
         <v>1415</v>
       </c>
@@ -17410,7 +22161,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="100" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C100" s="27" t="s">
         <v>1416</v>
       </c>
@@ -17427,7 +22178,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="101" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C101" s="27" t="s">
         <v>1417</v>
       </c>
@@ -17444,7 +22195,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="102" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C102" s="27" t="s">
         <v>1418</v>
       </c>
@@ -17461,7 +22212,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C103" s="27" t="s">
         <v>1419</v>
       </c>
@@ -17478,7 +22229,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="104" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C104" s="27" t="s">
         <v>1420</v>
       </c>
@@ -17692,7 +22443,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="130" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C130" s="42" t="s">
         <v>1453</v>
       </c>
@@ -17712,7 +22463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="3:8" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C131" s="42" t="s">
         <v>1454</v>
       </c>
@@ -17732,7 +22483,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="3:8" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C132" s="42" t="s">
         <v>1455</v>
       </c>
@@ -17772,7 +22523,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="134" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C134" s="43" t="s">
         <v>1457</v>
       </c>
@@ -17792,7 +22543,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="135" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C135" s="43" t="s">
         <v>1463</v>
       </c>
@@ -17812,7 +22563,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="136" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C136" s="42" t="s">
         <v>1448</v>
       </c>
@@ -17832,7 +22583,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="137" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C137" s="43" t="s">
         <v>1474</v>
       </c>
@@ -17852,7 +22603,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="138" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C138" s="42" t="s">
         <v>1480</v>
       </c>
@@ -17872,7 +22623,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="139" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="3:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C139" s="43" t="s">
         <v>1482</v>
       </c>
@@ -17892,7 +22643,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="140" spans="3:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="C140" s="44" t="s">
         <v>1486</v>
       </c>
@@ -17912,7 +22663,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C145" s="19" t="s">
         <v>1303</v>
       </c>
@@ -17929,7 +22680,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C146" t="s">
         <v>1307</v>
       </c>
@@ -17946,7 +22697,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C147" t="s">
         <v>1497</v>
       </c>
@@ -17963,7 +22714,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C148" t="s">
         <v>1501</v>
       </c>
@@ -17980,7 +22731,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C149" t="s">
         <v>1318</v>
       </c>
@@ -17997,7 +22748,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C150" t="s">
         <v>1322</v>
       </c>
@@ -18014,7 +22765,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C151" t="s">
         <v>1326</v>
       </c>
@@ -18031,7 +22782,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C152" t="s">
         <v>1518</v>
       </c>
@@ -18048,7 +22799,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C153" t="s">
         <v>1331</v>
       </c>
@@ -18065,7 +22816,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C154" t="s">
         <v>1523</v>
       </c>
@@ -18082,7 +22833,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C155" t="s">
         <v>1527</v>
       </c>
@@ -18099,7 +22850,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C156" t="s">
         <v>1531</v>
       </c>
@@ -18108,12 +22859,72 @@
       </c>
       <c r="G156" t="s">
         <v>1533</v>
+      </c>
+    </row>
+    <row r="160" spans="3:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C160" s="28" t="s">
+        <v>592</v>
+      </c>
+      <c r="D160" s="28" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E160" s="28" t="s">
+        <v>1534</v>
+      </c>
+      <c r="F160" s="28" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G160" s="28" t="s">
+        <v>649</v>
+      </c>
+      <c r="H160" s="28" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="161" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C161" s="27" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D161" s="27" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E161" s="27" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F161" s="27" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G161" s="27" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H161" s="27" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="162" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C162" s="27" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D162" s="27" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E162" s="27" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F162" s="27" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G162" s="27" t="s">
+        <v>1546</v>
+      </c>
+      <c r="H162" s="27" t="s">
+        <v>1548</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="13">
+  <tableParts count="15">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -18127,6 +22938,1032 @@
     <tablePart r:id="rId11"/>
     <tablePart r:id="rId12"/>
     <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4972632E-A7AF-4F0F-94E0-AC056960B122}">
+  <dimension ref="B3:H91"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B3" s="28" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B4" s="27" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="27" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B6" s="27" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="27" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="27" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F8" s="27"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="19" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="19" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D24" t="s">
+        <v>646</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D31" t="s">
+        <v>646</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D36" t="s">
+        <v>646</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D37" t="s">
+        <v>646</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D38" t="s">
+        <v>646</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="20" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B65" s="28" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G65" s="28" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H65" s="28" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B66" s="27" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="F66" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="G66" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="H66" s="27" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" s="27" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C67" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="D67" s="27" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F67" s="27" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G67" s="27" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H67" s="27" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68" s="27" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C68" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E68" s="27" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F68" s="27" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G68" s="27" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H68" s="27" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" s="27" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C69" s="27" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F69" s="27" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G69" s="27" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H69" s="27" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B70" s="27" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C70" s="27" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E70" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F70" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G70" s="27" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H70" s="27" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B73" s="19" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>637</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G73" s="19" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H73" s="19" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74">
+        <v>6</v>
+      </c>
+      <c r="F74">
+        <v>10</v>
+      </c>
+      <c r="G74">
+        <v>16</v>
+      </c>
+      <c r="H74">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75">
+        <v>8</v>
+      </c>
+      <c r="F75">
+        <v>15</v>
+      </c>
+      <c r="G75">
+        <v>20</v>
+      </c>
+      <c r="H75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>8</v>
+      </c>
+      <c r="H76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D77">
+        <v>7</v>
+      </c>
+      <c r="E77">
+        <v>17</v>
+      </c>
+      <c r="F77">
+        <v>30</v>
+      </c>
+      <c r="G77">
+        <v>44</v>
+      </c>
+      <c r="H77">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E78" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F78" t="s">
+        <v>1662</v>
+      </c>
+      <c r="G78" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E79" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F79" t="s">
+        <v>1666</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1667</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E80" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F80" t="s">
+        <v>1671</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1672</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F81" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H81" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F82" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H82" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C86" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D86">
+        <v>20570</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C87" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D87" t="e">
+        <f>+D86+D68</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C88" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C89" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C90" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C91" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="6">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>